--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2545,6 +2545,44 @@
       </c>
       <c r="F56" t="n">
         <v>77200.921875</v>
+      </c>
+      <c r="G56" t="n">
+        <v>77201.40625</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.484375</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.0006274173276474481</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.1081275643510731</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:31:02</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>24</v>
+      </c>
+      <c r="F57" t="n">
+        <v>77153.1484375</v>
       </c>
     </row>
   </sheetData>
@@ -2558,7 +2596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5949,6 +5987,24 @@
           <t>77194.359375,77203.578125,77234.007812,77228.101562,77235.054688,77203.328125,77216.500000,77218.890625,77197.593750,77173.281250,77203.734375,77170.046875,77189.382812,77149.773438,77185.726562,77159.625000,77172.273438,77169.953125,77183.320312,77178.671875,77166.007812,77193.640625,77188.062500,77200.921875</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>77200.000000,77279.046875,77257.000000,77340.726562,77336.023438,77311.710938,77339.796875,77319.453125,77351.601562,77438.648438,77363.968750,77337.968750,77191.421875,77126.281250,77105.429688,77152.679688,77240.789062,77219.859375,77266.421875,77252.960938,77299.531250,77268.023438,77176.070312,77201.406250</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>5.640625,75.468750,22.992188,112.625001,100.968749,108.382812,123.296875,100.562500,154.007812,265.367188,160.234375,167.921875,2.039063,23.492188,80.296874,6.945312,68.515624,49.906250,83.101563,74.289062,133.523438,74.382812,11.992188,0.484375</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>0.007307,0.097657,0.029761,0.145622,0.130558,0.140189,0.159422,0.130061,0.199101,0.342681,0.207118,0.217127,0.002642,0.030459,0.104139,0.009002,0.088704,0.064629,0.107552,0.096163,0.172735,0.096266,0.015539,0.000627</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0.1081275643510731</v>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>77205.851562,77243.406250,77206.921875,77277.820312,77271.640625,77268.773438,77213.359375,77179.062500,77131.843750,77272.726562,77192.460938,77217.007812,77152.968750,77210.546875,77276.828125,77239.226562,77246.968750,77226.593750,77285.609375,77250.429688,77294.617188,77184.468750,77281.875000,77234.203125</t>
@@ -5962,6 +6018,49 @@
       <c r="M56" t="inlineStr">
         <is>
           <t>77072.000000,76998.757812,76982.468750,76941.257812,76894.976562,76830.164062,76827.937500,76828.164062,76834.898438,76728.343750,76693.171875,76666.468750,76654.640625,76578.000000,76653.625000,76575.023438,76524.359375,76441.593750,76424.515625,76402.960938,76427.718750,76385.695312,76404.898438,76411.585938</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:31:02</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>24</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>77158.632812,77174.257812,77198.632812,77203.406250,77202.656250,77192.382812,77218.281250,77196.796875,77185.492188,77196.453125,77192.929688,77184.976562,77202.835938,77170.453125,77176.445312,77187.695312,77189.007812,77166.820312,77157.148438,77202.320312,77183.203125,77170.023438,77162.476562,77153.148438</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>77165.937500,77210.507812,77151.726562,77232.210938,77308.718750,77243.859375,77236.164062,77096.328125,77176.554688,77243.984375,77177.031250,77231.375000,77261.718750,77217.000000,77186.937500,77150.625000,77242.406250,77286.234375,77259.078125,77226.914062,77179.867188,77051.109375,77220.203125,77167.000000</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>76958.843750,76988.992188,76930.726562,76978.367188,76911.218750,76895.945312,76950.664062,76834.304688,76727.609375,76678.335938,76632.054688,76586.554688,76511.312500,76512.296875,76511.617188,76413.085938,76392.296875,76346.734375,76201.593750,76237.046875,76233.023438,76222.250000,76197.117188,76123.828125</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>77081.125000,77044.328125,77021.367188,77023.539062,77010.726562,76997.023438,77000.617188,76968.140625,76947.890625,76885.515625,76808.859375,76812.218750,76816.015625,76751.687500,76802.250000,76751.039062,76712.601562,76675.453125,76632.750000,76690.851562,76670.718750,76625.812500,76625.296875,76617.796875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2583,6 +2583,44 @@
       </c>
       <c r="F57" t="n">
         <v>77153.1484375</v>
+      </c>
+      <c r="G57" t="n">
+        <v>77543.7890625</v>
+      </c>
+      <c r="H57" t="n">
+        <v>390.640625</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.503767780402303</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.3422344638195667</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-14 04:37:22</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>24</v>
+      </c>
+      <c r="F58" t="n">
+        <v>77437.5234375</v>
       </c>
     </row>
   </sheetData>
@@ -2596,7 +2634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6048,6 +6086,24 @@
           <t>77158.632812,77174.257812,77198.632812,77203.406250,77202.656250,77192.382812,77218.281250,77196.796875,77185.492188,77196.453125,77192.929688,77184.976562,77202.835938,77170.453125,77176.445312,77187.695312,77189.007812,77166.820312,77157.148438,77202.320312,77183.203125,77170.023438,77162.476562,77153.148438</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>77291.429688,77099.742188,77100.179688,76778.023438,76766.093750,76623.929688,76759.132812,76730.140625,76818.078125,77177.820312,77105.273438,77256.648438,77298.593750,77312.343750,77253.718750,77313.468750,77280.578125,76676.039062,76799.851562,76767.398438,77076.828125,77569.132812,77566.500000,77543.789062</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>132.796876,74.515624,98.453124,425.382812,436.562500,568.453124,459.148438,466.656250,367.414063,18.632812,87.656251,71.671876,95.757812,141.890625,77.273438,125.773438,91.570313,490.781249,357.296876,434.921874,106.375000,399.109374,404.023438,390.640624</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>0.171813,0.096648,0.127695,0.554042,0.568692,0.741874,0.598168,0.608179,0.478291,0.024143,0.113684,0.092771,0.123880,0.183529,0.100026,0.162680,0.118491,0.640071,0.465231,0.566545,0.138012,0.514521,0.520874,0.503768</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0.3422344638195667</v>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>77165.937500,77210.507812,77151.726562,77232.210938,77308.718750,77243.859375,77236.164062,77096.328125,77176.554688,77243.984375,77177.031250,77231.375000,77261.718750,77217.000000,77186.937500,77150.625000,77242.406250,77286.234375,77259.078125,77226.914062,77179.867188,77051.109375,77220.203125,77167.000000</t>
@@ -6061,6 +6117,49 @@
       <c r="M57" t="inlineStr">
         <is>
           <t>77081.125000,77044.328125,77021.367188,77023.539062,77010.726562,76997.023438,77000.617188,76968.140625,76947.890625,76885.515625,76808.859375,76812.218750,76816.015625,76751.687500,76802.250000,76751.039062,76712.601562,76675.453125,76632.750000,76690.851562,76670.718750,76625.812500,76625.296875,76617.796875</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-14 04:37:22</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>24</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>77491.406250,77503.515625,77510.640625,77492.914062,77517.117188,77495.500000,77528.492188,77478.156250,77484.710938,77482.125000,77513.937500,77492.000000,77509.640625,77483.078125,77483.937500,77465.843750,77483.585938,77465.898438,77447.906250,77489.640625,77429.539062,77440.914062,77447.953125,77437.523438</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>77506.375000,77484.312500,77483.765625,77508.085938,77584.226562,77526.789062,77604.296875,77416.460938,77539.468750,77578.492188,77526.757812,77546.414062,77526.125000,77605.148438,77514.218750,77476.593750,77597.312500,77617.109375,77617.125000,77618.796875,77450.937500,77355.296875,77616.054688,77565.140625</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>77199.062500,77148.703125,77074.156250,77059.046875,76991.828125,76950.085938,76961.937500,76794.421875,76768.914062,76715.390625,76728.781250,76624.328125,76614.367188,76567.304688,76583.648438,76487.101562,76507.218750,76491.718750,76308.960938,76350.359375,76298.148438,76319.875000,76301.171875,76235.921875</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>77345.468750,77280.984375,77229.468750,77200.445312,77183.820312,77143.062500,77147.921875,77066.984375,77086.804688,77019.617188,76988.976562,76985.742188,76975.546875,76912.382812,76952.132812,76889.492188,76880.945312,76833.609375,76779.609375,76838.679688,76746.046875,76721.320312,76724.820312,76699.804688</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2621,6 +2621,44 @@
       </c>
       <c r="F58" t="n">
         <v>77437.5234375</v>
+      </c>
+      <c r="G58" t="n">
+        <v>77519.2578125</v>
+      </c>
+      <c r="H58" t="n">
+        <v>81.734375</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.1054375097317048</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.9025917386860899</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:37:50</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>24</v>
+      </c>
+      <c r="F59" t="n">
+        <v>77699.78125</v>
       </c>
     </row>
   </sheetData>
@@ -2634,7 +2672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6147,6 +6185,24 @@
           <t>77491.406250,77503.515625,77510.640625,77492.914062,77517.117188,77495.500000,77528.492188,77478.156250,77484.710938,77482.125000,77513.937500,77492.000000,77509.640625,77483.078125,77483.937500,77465.843750,77483.585938,77465.898438,77447.906250,77489.640625,77429.539062,77440.914062,77447.953125,77437.523438</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>77574.546875,77557.562500,77855.500000,77705.031250,78101.093750,77867.453125,77736.421875,77659.242188,78159.062500,78502.710938,78552.437500,78752.828125,78941.796875,79219.789062,78973.117188,79089.382812,78742.703125,78541.289062,78192.453125,77938.062500,77893.867188,77886.789062,77636.406250,77519.257812</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>83.140625,54.046875,344.859375,212.117188,583.976562,371.953125,207.929687,181.085938,674.351562,1020.585938,1038.500000,1260.828125,1432.156250,1736.710938,1489.179688,1623.539062,1259.117187,1075.390624,744.546875,448.421875,464.328126,445.875001,188.453125,81.734374</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>0.107175,0.069686,0.442948,0.272977,0.747719,0.477675,0.267480,0.233180,0.862794,1.300065,1.322047,1.600994,1.814193,2.192269,1.885679,2.052790,1.599027,1.369204,0.952198,0.575357,0.596104,0.572466,0.242738,0.105438</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>0.9025917386860899</v>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>77506.375000,77484.312500,77483.765625,77508.085938,77584.226562,77526.789062,77604.296875,77416.460938,77539.468750,77578.492188,77526.757812,77546.414062,77526.125000,77605.148438,77514.218750,77476.593750,77597.312500,77617.109375,77617.125000,77618.796875,77450.937500,77355.296875,77616.054688,77565.140625</t>
@@ -6160,6 +6216,49 @@
       <c r="M58" t="inlineStr">
         <is>
           <t>77345.468750,77280.984375,77229.468750,77200.445312,77183.820312,77143.062500,77147.921875,77066.984375,77086.804688,77019.617188,76988.976562,76985.742188,76975.546875,76912.382812,76952.132812,76889.492188,76880.945312,76833.609375,76779.609375,76838.679688,76746.046875,76721.320312,76724.820312,76699.804688</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:37:50</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>24</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>77488.250000,77488.289062,77508.109375,77529.656250,77527.250000,77512.710938,77556.523438,77582.257812,77594.359375,77621.125000,77676.781250,77696.281250,77735.835938,77714.789062,77741.031250,77735.328125,77760.734375,77756.359375,77722.937500,77734.351562,77696.921875,77704.320312,77684.625000,77699.781250</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>77505.617188,77470.343750,77512.265625,77562.265625,77587.242188,77593.953125,77649.828125,77561.875000,77603.031250,77682.859375,77684.617188,77723.578125,77671.835938,77795.734375,77730.695312,77728.453125,77804.281250,77763.328125,77736.890625,77719.593750,77642.382812,77567.960938,77731.273438,77696.398438</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>77204.046875,77118.546875,77026.156250,76994.226562,76858.945312,76793.039062,76788.523438,76691.250000,76699.960938,76646.867188,76737.710938,76688.593750,76689.671875,76660.335938,76678.085938,76615.757812,76603.328125,76582.109375,76400.875000,76388.781250,76374.625000,76333.718750,76337.023438,76314.742188</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>77328.875000,77250.101562,77180.187500,77165.406250,77089.046875,77039.195312,77076.906250,77028.164062,77095.750000,77009.828125,77039.406250,77089.664062,77089.875000,77041.812500,77110.218750,77067.875000,77050.710938,77008.359375,76959.671875,76946.734375,76905.875000,76892.093750,76827.437500,76822.375000</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2659,6 +2659,44 @@
       </c>
       <c r="F59" t="n">
         <v>77699.78125</v>
+      </c>
+      <c r="G59" t="n">
+        <v>75808.6328125</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1891.1484375</v>
+      </c>
+      <c r="I59" t="n">
+        <v>2.49463467066797</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.754670037484874</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-16 04:33:05</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>24</v>
+      </c>
+      <c r="F60" t="n">
+        <v>75524.8203125</v>
       </c>
     </row>
   </sheetData>
@@ -2672,7 +2710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6246,6 +6284,24 @@
           <t>77488.250000,77488.289062,77508.109375,77529.656250,77527.250000,77512.710938,77556.523438,77582.257812,77594.359375,77621.125000,77676.781250,77696.281250,77735.835938,77714.789062,77741.031250,77735.328125,77760.734375,77756.359375,77722.937500,77734.351562,77696.921875,77704.320312,77684.625000,77699.781250</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>77609.070312,77261.828125,76879.476562,76955.062500,76946.718750,77014.593750,76895.187500,76924.929688,76568.062500,75853.890625,76467.992188,76338.851562,76907.851562,75945.390625,76124.687500,75871.398438,75414.726562,75611.000000,75584.179688,75712.210938,75434.593750,75824.851562,75755.421875,75808.632812</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>120.820312,226.460937,628.632812,574.593750,580.531250,498.117188,661.335938,657.328124,1026.296875,1767.234375,1208.789062,1357.429688,827.984376,1769.398437,1616.343750,1863.929688,2346.007812,2145.359375,2138.757812,2022.140624,2262.328125,1879.468749,1929.203125,1891.148438</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0.155678,0.293108,0.817686,0.746661,0.754459,0.646783,0.860049,0.854506,1.340372,2.329787,1.580778,1.778164,1.076593,2.329830,2.123285,2.456696,3.110809,2.837364,2.829637,2.670825,2.999059,2.478698,2.546621,2.494635</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>1.754670037484874</v>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>77505.617188,77470.343750,77512.265625,77562.265625,77587.242188,77593.953125,77649.828125,77561.875000,77603.031250,77682.859375,77684.617188,77723.578125,77671.835938,77795.734375,77730.695312,77728.453125,77804.281250,77763.328125,77736.890625,77719.593750,77642.382812,77567.960938,77731.273438,77696.398438</t>
@@ -6259,6 +6315,49 @@
       <c r="M59" t="inlineStr">
         <is>
           <t>77328.875000,77250.101562,77180.187500,77165.406250,77089.046875,77039.195312,77076.906250,77028.164062,77095.750000,77009.828125,77039.406250,77089.664062,77089.875000,77041.812500,77110.218750,77067.875000,77050.710938,77008.359375,76959.671875,76946.734375,76905.875000,76892.093750,76827.437500,76822.375000</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-16 04:33:05</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>24</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>75815.109375,75779.804688,75791.250000,75756.390625,75791.148438,75754.140625,75744.539062,75710.867188,75707.539062,75695.734375,75681.453125,75667.234375,75663.640625,75657.281250,75681.093750,75649.203125,75628.960938,75625.109375,75583.437500,75595.750000,75594.460938,75567.531250,75529.828125,75524.820312</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>75831.687500,75854.625000,75738.375000,75814.992188,75791.781250,75851.226562,75772.242188,75647.718750,75813.218750,75792.351562,75745.218750,75717.601562,75732.445312,75798.132812,75716.492188,75606.718750,75678.625000,75705.648438,75719.039062,75663.390625,75605.062500,75480.687500,75667.750000,75700.781250</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>75427.312500,75297.632812,75210.906250,75132.648438,75087.601562,74993.257812,75002.304688,74840.070312,74811.398438,74713.593750,74714.289062,74673.343750,74580.390625,74503.468750,74508.601562,74402.875000,74352.273438,74310.773438,74115.171875,74122.429688,74161.203125,74094.125000,74083.218750,74048.562500</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>75603.000000,75490.023438,75430.468750,75351.195312,75358.421875,75303.187500,75313.015625,75203.421875,75251.890625,75131.820312,75079.312500,75116.921875,75028.101562,74973.507812,75022.210938,74922.031250,74897.468750,74800.242188,74758.898438,74770.210938,74752.929688,74702.562500,74668.835938,74658.062500</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2697,6 +2697,44 @@
       </c>
       <c r="F60" t="n">
         <v>75524.8203125</v>
+      </c>
+      <c r="G60" t="n">
+        <v>76206.0390625</v>
+      </c>
+      <c r="H60" t="n">
+        <v>681.21875</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.8939170154760331</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.3894400969205373</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:38:29</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>24</v>
+      </c>
+      <c r="F61" t="n">
+        <v>76062.328125</v>
       </c>
     </row>
   </sheetData>
@@ -2710,7 +2748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6345,6 +6383,24 @@
           <t>75815.109375,75779.804688,75791.250000,75756.390625,75791.148438,75754.140625,75744.539062,75710.867188,75707.539062,75695.734375,75681.453125,75667.234375,75663.640625,75657.281250,75681.093750,75649.203125,75628.960938,75625.109375,75583.437500,75595.750000,75594.460938,75567.531250,75529.828125,75524.820312</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>75905.898438,75969.000000,75695.031250,75670.390625,75924.039062,75885.507812,76182.140625,75901.218750,75582.093750,75618.976562,75729.312500,75701.601562,75778.437500,75552.617188,76010.210938,76101.460938,75907.460938,75620.078125,76143.960938,76273.320312,76296.812500,76303.742188,76364.562500,76206.039062</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>90.789062,189.195312,96.218750,86.000000,132.890624,131.367188,437.601563,190.351562,125.445312,76.757812,47.859375,34.367188,114.796875,104.664062,329.117188,452.257812,278.499999,5.031250,560.523438,677.570312,702.351562,736.210938,834.734375,681.218751</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>0.119607,0.249043,0.127114,0.113651,0.175031,0.173112,0.574415,0.250789,0.165972,0.101506,0.063198,0.045398,0.151490,0.138531,0.432991,0.594283,0.366894,0.006653,0.736136,0.888345,0.920552,0.964843,1.093091,0.893917</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>0.3894400969205373</v>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>75831.687500,75854.625000,75738.375000,75814.992188,75791.781250,75851.226562,75772.242188,75647.718750,75813.218750,75792.351562,75745.218750,75717.601562,75732.445312,75798.132812,75716.492188,75606.718750,75678.625000,75705.648438,75719.039062,75663.390625,75605.062500,75480.687500,75667.750000,75700.781250</t>
@@ -6358,6 +6414,49 @@
       <c r="M60" t="inlineStr">
         <is>
           <t>75603.000000,75490.023438,75430.468750,75351.195312,75358.421875,75303.187500,75313.015625,75203.421875,75251.890625,75131.820312,75079.312500,75116.921875,75028.101562,74973.507812,75022.210938,74922.031250,74897.468750,74800.242188,74758.898438,74770.210938,74752.929688,74702.562500,74668.835938,74658.062500</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:38:29</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>24</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>76210.656250,76203.398438,76208.671875,76185.398438,76214.093750,76230.679688,76216.312500,76226.226562,76194.187500,76201.921875,76208.250000,76187.195312,76149.562500,76168.351562,76151.992188,76150.382812,76114.234375,76113.078125,76097.828125,76106.460938,76078.382812,76091.140625,76063.828125,76062.328125</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>76177.812500,76203.234375,76203.687500,76199.296875,76166.601562,76251.343750,76213.390625,76195.382812,76209.609375,76257.148438,76236.523438,76196.226562,76200.656250,76219.593750,76194.984375,76191.226562,76147.679688,76186.390625,76175.820312,76186.281250,76106.703125,76040.703125,76106.187500,76174.484375</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>75899.562500,75802.125000,75722.875000,75639.562500,75626.421875,75573.078125,75512.398438,75447.773438,75394.429688,75307.343750,75280.015625,75199.343750,75129.640625,75116.312500,75070.437500,75020.984375,74948.765625,74919.632812,74812.882812,74752.703125,74766.914062,74740.664062,74700.203125,74669.500000</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>76014.960938,75946.546875,75908.898438,75835.742188,75816.406250,75816.015625,75792.500000,75754.992188,75749.031250,75637.343750,75588.625000,75593.062500,75524.335938,75503.875000,75496.382812,75492.867188,75444.289062,75339.773438,75348.601562,75315.898438,75287.351562,75276.742188,75252.148438,75238.484375</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2735,6 +2735,44 @@
       </c>
       <c r="F61" t="n">
         <v>76062.328125</v>
+      </c>
+      <c r="G61" t="n">
+        <v>77224.2578125</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1161.9296875</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.504617487320057</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.5275070292807253</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:23:45</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>24</v>
+      </c>
+      <c r="F62" t="n">
+        <v>77180.328125</v>
       </c>
     </row>
   </sheetData>
@@ -2748,7 +2786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6444,6 +6482,24 @@
           <t>76210.656250,76203.398438,76208.671875,76185.398438,76214.093750,76230.679688,76216.312500,76226.226562,76194.187500,76201.921875,76208.250000,76187.195312,76149.562500,76168.351562,76151.992188,76150.382812,76114.234375,76113.078125,76097.828125,76106.460938,76078.382812,76091.140625,76063.828125,76062.328125</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>76250.976562,76402.921875,76377.570312,76497.640625,76395.937500,76329.953125,76400.992188,76659.828125,76612.257812,76423.617188,76676.421875,76688.007812,76606.828125,76506.398438,76543.343750,76498.539062,76352.546875,76359.867188,76348.742188,76526.101562,76659.398438,76910.796875,77297.703125,77224.257812</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>40.320312,199.523437,168.898438,312.242187,181.843750,99.273437,184.679688,433.601563,418.070312,221.695312,468.171875,500.812501,457.265625,338.046876,391.351562,348.156251,238.312500,246.789062,250.914062,419.640624,581.015626,819.656250,1233.875000,1161.929688</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0.052878,0.261146,0.221136,0.408172,0.238028,0.130058,0.241724,0.565618,0.545696,0.290087,0.610581,0.653052,0.596899,0.441854,0.511281,0.455115,0.312121,0.323192,0.328642,0.548363,0.757918,1.065723,1.596263,1.504617</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>0.5275070292807253</v>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>76177.812500,76203.234375,76203.687500,76199.296875,76166.601562,76251.343750,76213.390625,76195.382812,76209.609375,76257.148438,76236.523438,76196.226562,76200.656250,76219.593750,76194.984375,76191.226562,76147.679688,76186.390625,76175.820312,76186.281250,76106.703125,76040.703125,76106.187500,76174.484375</t>
@@ -6457,6 +6513,49 @@
       <c r="M61" t="inlineStr">
         <is>
           <t>76014.960938,75946.546875,75908.898438,75835.742188,75816.406250,75816.015625,75792.500000,75754.992188,75749.031250,75637.343750,75588.625000,75593.062500,75524.335938,75503.875000,75496.382812,75492.867188,75444.289062,75339.773438,75348.601562,75315.898438,75287.351562,75276.742188,75252.148438,75238.484375</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:23:45</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>24</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>77181.359375,77194.492188,77172.046875,77169.960938,77171.664062,77191.250000,77188.664062,77202.070312,77193.140625,77209.312500,77203.406250,77193.015625,77187.453125,77182.890625,77173.890625,77183.953125,77180.523438,77176.421875,77173.101562,77168.578125,77165.515625,77169.000000,77176.898438,77180.328125</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>77179.609375,77185.078125,77199.156250,77195.648438,77163.265625,77186.437500,77216.203125,77197.453125,77213.078125,77205.320312,77222.578125,77246.820312,77228.718750,77223.531250,77206.835938,77242.445312,77233.570312,77273.390625,77253.250000,77234.187500,77189.335938,77195.312500,77232.296875,77232.335938</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>76844.804688,76768.968750,76664.617188,76613.890625,76556.640625,76534.710938,76488.078125,76425.148438,76417.546875,76348.484375,76354.171875,76258.171875,76263.656250,76197.750000,76188.718750,76142.031250,76095.789062,76070.898438,75956.460938,75901.492188,75881.585938,75848.953125,75857.914062,75836.656250</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>76981.718750,76940.390625,76863.976562,76830.765625,76789.937500,76782.265625,76781.117188,76740.828125,76732.632812,76664.414062,76632.875000,76641.546875,76603.390625,76551.750000,76566.890625,76561.664062,76524.406250,76474.250000,76449.398438,76409.687500,76379.460938,76365.609375,76386.406250,76368.906250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2773,6 +2773,44 @@
       </c>
       <c r="F62" t="n">
         <v>77180.328125</v>
+      </c>
+      <c r="G62" t="n">
+        <v>81112.4609375</v>
+      </c>
+      <c r="H62" t="n">
+        <v>3932.1328125</v>
+      </c>
+      <c r="I62" t="n">
+        <v>4.847754299465586</v>
+      </c>
+      <c r="J62" t="n">
+        <v>3.461574499600738</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:20:39</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>24</v>
+      </c>
+      <c r="F63" t="n">
+        <v>80432.90625</v>
       </c>
     </row>
   </sheetData>
@@ -2786,7 +2824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6543,6 +6581,24 @@
           <t>77181.359375,77194.492188,77172.046875,77169.960938,77171.664062,77191.250000,77188.664062,77202.070312,77193.140625,77209.312500,77203.406250,77193.015625,77187.453125,77182.890625,77173.890625,77183.953125,77180.523438,77176.421875,77173.101562,77168.578125,77165.515625,77169.000000,77176.898438,77180.328125</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>77426.773438,77527.382812,77734.781250,78200.000000,78148.140625,78221.460938,77995.187500,77979.593750,80026.992188,80904.093750,80698.242188,80829.000000,80992.593750,80916.382812,81180.000000,81096.187500,81223.781250,81124.523438,80875.101562,81654.632812,81262.507812,81261.007812,81105.031250,81112.460938</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>245.414062,332.890624,562.734375,1030.039062,976.476563,1030.210938,806.523438,777.523438,2833.851562,3694.781250,3494.835938,3635.984375,3805.140625,3733.492188,4006.109375,3912.234375,4043.257812,3948.101562,3702.000001,4486.054688,4096.992188,4092.007812,3928.132812,3932.132812</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>0.316963,0.429385,0.723916,1.317186,1.249520,1.317044,1.034068,0.997086,3.541120,4.566866,4.330746,4.498366,4.698134,4.614013,4.934848,4.824190,4.977924,4.866718,4.577429,5.493938,5.041676,5.035635,4.843267,4.847754</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>3.461574499600738</v>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>77179.609375,77185.078125,77199.156250,77195.648438,77163.265625,77186.437500,77216.203125,77197.453125,77213.078125,77205.320312,77222.578125,77246.820312,77228.718750,77223.531250,77206.835938,77242.445312,77233.570312,77273.390625,77253.250000,77234.187500,77189.335938,77195.312500,77232.296875,77232.335938</t>
@@ -6556,6 +6612,49 @@
       <c r="M62" t="inlineStr">
         <is>
           <t>76981.718750,76940.390625,76863.976562,76830.765625,76789.937500,76782.265625,76781.117188,76740.828125,76732.632812,76664.414062,76632.875000,76641.546875,76603.390625,76551.750000,76566.890625,76561.664062,76524.406250,76474.250000,76449.398438,76409.687500,76379.460938,76365.609375,76386.406250,76368.906250</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:20:39</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>24</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>81084.921875,81053.335938,81025.164062,80993.578125,80949.656250,80949.718750,80921.718750,80910.875000,80902.554688,80891.968750,80851.804688,80794.750000,80744.273438,80714.968750,80685.664062,80636.648438,80645.984375,80567.593750,80531.476562,80476.578125,80482.156250,80466.757812,80446.109375,80432.906250</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>81047.195312,80982.703125,80973.757812,80951.507812,80852.945312,80811.046875,80726.078125,80808.609375,80707.460938,80747.007812,80667.929688,80550.937500,80450.484375,80556.453125,80448.437500,80533.351562,80364.906250,80329.429688,80226.968750,80295.125000,80242.046875,80350.187500,80254.781250,80165.593750</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>80651.945312,80522.984375,80355.484375,80199.703125,80053.296875,79935.156250,79792.710938,79722.875000,79658.781250,79601.234375,79482.968750,79399.718750,79376.734375,79257.695312,79133.703125,79081.195312,79027.359375,78945.890625,78791.796875,78640.234375,78636.906250,78579.515625,78530.976562,78525.148438</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>80837.898438,80729.367188,80602.609375,80524.890625,80389.109375,80322.296875,80244.867188,80174.031250,80151.492188,80102.109375,80030.500000,79986.609375,79888.203125,79838.796875,79752.914062,79712.484375,79688.421875,79604.726562,79511.101562,79445.734375,79420.890625,79328.250000,79319.882812,79303.398438</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2811,6 +2811,44 @@
       </c>
       <c r="F63" t="n">
         <v>80432.90625</v>
+      </c>
+      <c r="G63" t="n">
+        <v>80442.4296875</v>
+      </c>
+      <c r="H63" t="n">
+        <v>9.5234375</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.01183882378614908</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.5423046456033833</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-20 04:39:41</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>24</v>
+      </c>
+      <c r="F64" t="n">
+        <v>80060.453125</v>
       </c>
     </row>
   </sheetData>
@@ -2824,7 +2862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6642,6 +6680,24 @@
           <t>81084.921875,81053.335938,81025.164062,80993.578125,80949.656250,80949.718750,80921.718750,80910.875000,80902.554688,80891.968750,80851.804688,80794.750000,80744.273438,80714.968750,80685.664062,80636.648438,80645.984375,80567.593750,80531.476562,80476.578125,80482.156250,80466.757812,80446.109375,80432.906250</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>81022.500000,81013.562500,81061.148438,81297.648438,81298.843750,81189.601562,81280.000000,81309.992188,81325.000000,81554.890625,81610.820312,81813.351562,81437.101562,81412.242188,81344.023438,81129.976562,81063.726562,81232.468750,81276.359375,81277.492188,81071.710938,80312.476562,80458.390625,80442.429688</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>62.421875,39.773438,35.984376,304.070312,349.187500,239.882812,358.281250,399.117188,422.445312,662.921875,759.015624,1018.601562,692.828124,697.273438,658.359376,493.328124,417.742188,664.875000,744.882813,800.914062,589.554688,154.281249,12.281250,9.523438</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>0.077043,0.049095,0.044392,0.374021,0.429511,0.295460,0.440799,0.490859,0.519453,0.812854,0.930043,1.245031,0.850752,0.856472,0.809352,0.608071,0.515326,0.818484,0.916482,0.985407,0.727201,0.192101,0.015264,0.011839</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>0.5423046456033833</v>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>81047.195312,80982.703125,80973.757812,80951.507812,80852.945312,80811.046875,80726.078125,80808.609375,80707.460938,80747.007812,80667.929688,80550.937500,80450.484375,80556.453125,80448.437500,80533.351562,80364.906250,80329.429688,80226.968750,80295.125000,80242.046875,80350.187500,80254.781250,80165.593750</t>
@@ -6655,6 +6711,49 @@
       <c r="M63" t="inlineStr">
         <is>
           <t>80837.898438,80729.367188,80602.609375,80524.890625,80389.109375,80322.296875,80244.867188,80174.031250,80151.492188,80102.109375,80030.500000,79986.609375,79888.203125,79838.796875,79752.914062,79712.484375,79688.421875,79604.726562,79511.101562,79445.734375,79420.890625,79328.250000,79319.882812,79303.398438</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-20 04:39:41</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>24</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>80454.554688,80445.234375,80431.023438,80431.265625,80417.812500,80396.593750,80427.164062,80401.992188,80399.500000,80388.078125,80348.625000,80297.156250,80301.382812,80294.632812,80269.859375,80250.437500,80245.578125,80213.460938,80197.734375,80167.492188,80130.984375,80125.109375,80093.671875,80060.453125</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>80413.726562,80437.460938,80370.085938,80412.476562,80369.218750,80288.320312,80345.656250,80315.585938,80337.132812,80309.078125,80278.671875,80184.750000,80178.781250,80199.867188,80162.578125,80261.703125,80124.343750,80097.921875,80092.539062,80091.406250,80018.390625,80038.343750,80041.921875,79980.304688</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>80052.515625,79953.234375,79833.484375,79738.750000,79646.390625,79546.218750,79476.265625,79399.703125,79367.250000,79310.085938,79232.453125,79157.398438,79172.406250,79089.906250,78956.664062,78911.789062,78854.171875,78811.882812,78655.882812,78573.468750,78543.335938,78521.585938,78464.234375,78400.828125</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>80228.843750,80153.546875,80060.320312,80024.164062,79954.382812,79880.523438,79858.640625,79794.328125,79790.476562,79739.703125,79676.773438,79642.382812,79593.250000,79558.031250,79468.117188,79442.078125,79389.281250,79343.757812,79265.867188,79232.453125,79177.148438,79138.984375,79115.656250,79062.421875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2849,6 +2849,44 @@
       </c>
       <c r="F64" t="n">
         <v>80060.453125</v>
+      </c>
+      <c r="G64" t="n">
+        <v>81346.4765625</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1286.0234375</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1.580920885383308</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.7485417868381886</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-21 04:37:38</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>24</v>
+      </c>
+      <c r="F65" t="n">
+        <v>81039.2890625</v>
       </c>
     </row>
   </sheetData>
@@ -2862,7 +2900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6741,6 +6779,24 @@
           <t>80454.554688,80445.234375,80431.023438,80431.265625,80417.812500,80396.593750,80427.164062,80401.992188,80399.500000,80388.078125,80348.625000,80297.156250,80301.382812,80294.632812,80269.859375,80250.437500,80245.578125,80213.460938,80197.734375,80167.492188,80130.984375,80125.109375,80093.671875,80060.453125</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>80456.007812,80272.500000,80284.562500,80228.203125,80430.007812,80283.007812,80442.976562,80451.140625,80522.046875,80639.539062,80874.203125,81311.992188,81129.328125,81021.218750,81162.437500,81073.468750,80916.046875,81196.492188,81159.539062,81604.820312,80981.781250,81299.859375,81411.500000,81346.476562</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>1.453124,172.734375,146.460938,203.062500,12.195312,113.585938,15.812501,49.148437,122.546875,251.460938,525.578125,1014.835938,827.945313,726.585938,892.578125,823.031250,670.468750,983.031249,961.804688,1437.328124,850.796875,1174.750000,1317.828125,1286.023438</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>0.001806,0.215185,0.182427,0.253106,0.015163,0.141482,0.019657,0.061091,0.152190,0.311833,0.649871,1.248077,1.020525,0.896785,1.099743,1.015167,0.828598,1.210682,1.185079,1.761327,1.050603,1.444959,1.618725,1.580921</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>0.7485417868381886</v>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>80413.726562,80437.460938,80370.085938,80412.476562,80369.218750,80288.320312,80345.656250,80315.585938,80337.132812,80309.078125,80278.671875,80184.750000,80178.781250,80199.867188,80162.578125,80261.703125,80124.343750,80097.921875,80092.539062,80091.406250,80018.390625,80038.343750,80041.921875,79980.304688</t>
@@ -6754,6 +6810,49 @@
       <c r="M64" t="inlineStr">
         <is>
           <t>80228.843750,80153.546875,80060.320312,80024.164062,79954.382812,79880.523438,79858.640625,79794.328125,79790.476562,79739.703125,79676.773438,79642.382812,79593.250000,79558.031250,79468.117188,79442.078125,79389.281250,79343.757812,79265.867188,79232.453125,79177.148438,79138.984375,79115.656250,79062.421875</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-21 04:37:38</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>24</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>81363.031250,81354.687500,81339.812500,81351.171875,81348.632812,81357.976562,81342.226562,81309.750000,81309.828125,81283.812500,81286.289062,81301.890625,81277.750000,81258.218750,81252.937500,81204.906250,81207.757812,81165.484375,81159.906250,81116.632812,81119.492188,81073.859375,81078.648438,81039.289062</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>81329.187500,81316.570312,81341.726562,81300.406250,81333.250000,81278.546875,81215.562500,81278.953125,81203.953125,81175.585938,81195.468750,81195.828125,81179.859375,81155.515625,81140.312500,81171.382812,80999.507812,81023.507812,81008.218750,80928.718750,80898.664062,80998.515625,80934.882812,80840.125000</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>81013.515625,80927.382812,80794.828125,80767.007812,80693.085938,80643.835938,80575.476562,80488.609375,80427.062500,80338.625000,80295.523438,80277.734375,80212.718750,80135.671875,80043.976562,79976.710938,79886.054688,79846.656250,79718.828125,79590.101562,79617.125000,79537.296875,79478.875000,79405.000000</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>81159.625000,81114.320312,81016.250000,80998.648438,80951.320312,80931.796875,80906.937500,80838.039062,80800.632812,80736.031250,80692.992188,80717.484375,80643.515625,80574.132812,80509.062500,80493.265625,80402.453125,80377.593750,80293.578125,80246.304688,80224.484375,80168.359375,80150.875000,80084.898438</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,6 +2887,44 @@
       </c>
       <c r="F65" t="n">
         <v>81039.2890625</v>
+      </c>
+      <c r="G65" t="n">
+        <v>85476.6328125</v>
+      </c>
+      <c r="H65" t="n">
+        <v>4437.34375</v>
+      </c>
+      <c r="I65" t="n">
+        <v>5.191294514061728</v>
+      </c>
+      <c r="J65" t="n">
+        <v>4.589354055591271</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-22 04:33:35</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>24</v>
+      </c>
+      <c r="F66" t="n">
+        <v>84160.546875</v>
       </c>
     </row>
   </sheetData>
@@ -2900,7 +2938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6840,6 +6878,24 @@
           <t>81363.031250,81354.687500,81339.812500,81351.171875,81348.632812,81357.976562,81342.226562,81309.750000,81309.828125,81283.812500,81286.289062,81301.890625,81277.750000,81258.218750,81252.937500,81204.906250,81207.757812,81165.484375,81159.906250,81116.632812,81119.492188,81073.859375,81078.648438,81039.289062</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>81541.937500,81621.539062,81706.867188,83751.796875,84637.289062,84416.578125,84863.609375,85317.320312,85432.117188,85834.523438,85933.156250,85968.953125,85902.117188,86071.781250,86501.828125,86989.898438,86557.296875,86423.117188,86591.750000,85879.500000,85598.656250,85700.000000,85675.000000,85476.632812</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>178.906250,266.851562,367.054688,2400.625000,3288.656251,3058.601563,3521.382813,4007.570312,4122.289062,4550.710938,4646.867188,4667.062500,4624.367188,4813.562500,5248.890625,5784.992188,5349.539063,5257.632812,5431.843750,4762.867188,4479.164062,4626.140625,4596.351562,4437.343751</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>0.219404,0.326938,0.449234,2.866356,3.885588,3.623224,4.149462,4.697253,4.825222,5.301726,5.407537,5.428777,5.383298,5.592498,6.067953,6.650188,6.180344,6.083595,6.272934,5.545988,5.232750,5.398064,5.364869,5.191295</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>4.589354055591271</v>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>81329.187500,81316.570312,81341.726562,81300.406250,81333.250000,81278.546875,81215.562500,81278.953125,81203.953125,81175.585938,81195.468750,81195.828125,81179.859375,81155.515625,81140.312500,81171.382812,80999.507812,81023.507812,81008.218750,80928.718750,80898.664062,80998.515625,80934.882812,80840.125000</t>
@@ -6853,6 +6909,49 @@
       <c r="M65" t="inlineStr">
         <is>
           <t>81159.625000,81114.320312,81016.250000,80998.648438,80951.320312,80931.796875,80906.937500,80838.039062,80800.632812,80736.031250,80692.992188,80717.484375,80643.515625,80574.132812,80509.062500,80493.265625,80402.453125,80377.593750,80293.578125,80246.304688,80224.484375,80168.359375,80150.875000,80084.898438</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-22 04:33:35</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>24</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>85463.796875,85351.132812,85320.242188,85295.968750,85214.773438,85144.843750,85128.406250,85069.343750,85023.375000,84994.695312,84900.812500,84813.726562,84756.437500,84681.554688,84622.546875,84594.414062,84624.546875,84527.000000,84493.164062,84336.664062,84362.484375,84286.968750,84230.226562,84160.546875</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>85303.828125,85232.062500,85300.109375,85226.375000,85119.500000,84929.000000,84848.875000,84883.476562,84811.687500,84748.304688,84670.984375,84484.429688,84344.171875,84322.406250,84343.468750,84366.421875,84254.054688,84210.757812,84136.156250,83957.531250,83996.476562,84079.140625,83823.218750,83751.476562</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>84660.140625,84452.343750,84264.632812,84108.265625,83890.750000,83692.898438,83480.781250,83302.046875,83180.867188,83059.750000,82844.609375,82671.015625,82646.289062,82450.968750,82268.781250,82210.187500,82058.093750,81941.078125,81669.257812,81366.039062,81357.218750,81180.226562,81046.937500,81008.875000</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>84995.070312,84830.609375,84684.929688,84616.046875,84451.359375,84283.765625,84213.257812,84063.148438,83968.476562,83885.312500,83712.945312,83622.890625,83485.007812,83364.046875,83218.812500,83227.500000,83132.617188,82991.445312,82848.500000,82650.781250,82612.070312,82441.085938,82352.500000,82276.390625</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2925,6 +2925,44 @@
       </c>
       <c r="F66" t="n">
         <v>84160.546875</v>
+      </c>
+      <c r="G66" t="n">
+        <v>87022.3203125</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2861.7734375</v>
+      </c>
+      <c r="I66" t="n">
+        <v>3.288551060490318</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1.626115673966701</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-23 04:30:00</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>24</v>
+      </c>
+      <c r="F67" t="n">
+        <v>86738.9453125</v>
       </c>
     </row>
   </sheetData>
@@ -2938,7 +2976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6939,6 +6977,24 @@
           <t>85463.796875,85351.132812,85320.242188,85295.968750,85214.773438,85144.843750,85128.406250,85069.343750,85023.375000,84994.695312,84900.812500,84813.726562,84756.437500,84681.554688,84622.546875,84594.414062,84624.546875,84527.000000,84493.164062,84336.664062,84362.484375,84286.968750,84230.226562,84160.546875</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>85392.796875,85359.226562,85333.500000,86198.789062,86238.820312,85875.023438,85969.070312,86008.429688,86328.789062,86255.257812,86418.453125,86451.609375,86587.578125,86469.578125,86236.921875,86262.570312,86187.023438,86121.859375,86198.046875,86451.929688,86366.468750,86544.210938,86696.406250,87022.320312</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>71.000000,8.093751,13.257812,902.820312,1024.046874,730.179688,840.664062,939.085938,1305.414062,1260.562501,1517.640625,1637.882813,1831.140625,1788.023437,1614.375000,1668.156251,1562.476562,1594.859375,1704.882813,2115.265626,2003.984375,2257.242188,2466.179688,2861.773438</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>0.083145,0.009482,0.015536,1.047370,1.187455,0.850282,0.977868,1.091853,1.512142,1.461433,1.756153,1.894566,2.114784,2.067806,1.872023,1.933812,1.812891,1.851864,1.977867,2.446754,2.320327,2.608195,2.844616,3.288551</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>1.626115673966701</v>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>85303.828125,85232.062500,85300.109375,85226.375000,85119.500000,84929.000000,84848.875000,84883.476562,84811.687500,84748.304688,84670.984375,84484.429688,84344.171875,84322.406250,84343.468750,84366.421875,84254.054688,84210.757812,84136.156250,83957.531250,83996.476562,84079.140625,83823.218750,83751.476562</t>
@@ -6952,6 +7008,49 @@
       <c r="M66" t="inlineStr">
         <is>
           <t>84995.070312,84830.609375,84684.929688,84616.046875,84451.359375,84283.765625,84213.257812,84063.148438,83968.476562,83885.312500,83712.945312,83622.890625,83485.007812,83364.046875,83218.812500,83227.500000,83132.617188,82991.445312,82848.500000,82650.781250,82612.070312,82441.085938,82352.500000,82276.390625</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-23 04:30:00</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>24</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>87000.804688,87048.531250,87057.968750,87116.234375,87105.109375,87101.570312,87109.828125,87081.179688,87077.625000,87025.820312,86951.406250,86934.664062,86857.226562,86849.906250,86858.437500,86887.140625,86882.476562,86811.828125,86807.195312,86739.484375,86775.468750,86732.593750,86749.367188,86738.945312</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>86879.968750,86955.101562,86972.671875,87123.218750,87147.523438,86968.070312,86917.132812,87011.109375,86942.000000,86817.593750,86769.421875,86670.804688,86663.015625,86635.554688,86613.593750,86767.484375,86574.289062,86604.328125,86587.406250,86457.578125,86542.265625,86527.093750,86375.109375,86436.070312</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>86568.882812,86542.125000,86410.453125,86390.242188,86292.046875,86181.515625,86056.093750,85971.523438,85901.156250,85781.343750,85585.421875,85486.687500,85396.125000,85272.421875,85129.234375,85147.757812,84998.765625,84903.046875,84720.054688,84499.195312,84479.531250,84380.343750,84328.203125,84350.078125</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>86768.218750,86768.500000,86691.453125,86737.312500,86646.250000,86588.375000,86585.289062,86497.562500,86455.140625,86362.781250,86194.664062,86180.187500,86053.914062,85973.281250,85887.695312,85944.796875,85845.343750,85761.398438,85663.585938,85544.445312,85537.562500,85406.531250,85446.968750,85436.968750</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2963,6 +2963,44 @@
       </c>
       <c r="F67" t="n">
         <v>86738.9453125</v>
+      </c>
+      <c r="G67" t="n">
+        <v>83867.21875</v>
+      </c>
+      <c r="H67" t="n">
+        <v>2871.7265625</v>
+      </c>
+      <c r="I67" t="n">
+        <v>3.424134727849193</v>
+      </c>
+      <c r="J67" t="n">
+        <v>2.408761699147635</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:27:10</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>24</v>
+      </c>
+      <c r="F68" t="n">
+        <v>83421.171875</v>
       </c>
     </row>
   </sheetData>
@@ -2976,7 +3014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7038,6 +7076,24 @@
           <t>87000.804688,87048.531250,87057.968750,87116.234375,87105.109375,87101.570312,87109.828125,87081.179688,87077.625000,87025.820312,86951.406250,86934.664062,86857.226562,86849.906250,86858.437500,86887.140625,86882.476562,86811.828125,86807.195312,86739.484375,86775.468750,86732.593750,86749.367188,86738.945312</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>86485.632812,86456.523438,86128.156250,85901.812500,85848.859375,85906.656250,85632.039062,85482.101562,85780.117188,84521.351562,84001.882812,84027.109375,84312.828125,84313.007812,84509.820312,84235.351562,84400.000000,84551.289062,84369.007812,84309.453125,84095.109375,84349.882812,83928.156250,83867.218750</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>515.171876,592.007812,929.812500,1214.421875,1256.250000,1194.914062,1477.789062,1599.078126,1297.507812,2504.468749,2949.523438,2907.554687,2544.398437,2536.898438,2348.617188,2651.789062,2482.476562,2260.539062,2438.187499,2430.031250,2680.359375,2382.710938,2821.210938,2871.726562</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>0.595673,0.684746,1.079569,1.413733,1.463328,1.390945,1.725743,1.870658,1.512597,2.963120,3.511259,3.460258,3.017807,3.008905,2.779106,3.148071,2.941323,2.673571,2.889909,2.882276,3.187295,2.824795,3.361459,3.424135</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>2.408761699147635</v>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>86879.968750,86955.101562,86972.671875,87123.218750,87147.523438,86968.070312,86917.132812,87011.109375,86942.000000,86817.593750,86769.421875,86670.804688,86663.015625,86635.554688,86613.593750,86767.484375,86574.289062,86604.328125,86587.406250,86457.578125,86542.265625,86527.093750,86375.109375,86436.070312</t>
@@ -7051,6 +7107,49 @@
       <c r="M67" t="inlineStr">
         <is>
           <t>86768.218750,86768.500000,86691.453125,86737.312500,86646.250000,86588.375000,86585.289062,86497.562500,86455.140625,86362.781250,86194.664062,86180.187500,86053.914062,85973.281250,85887.695312,85944.796875,85845.343750,85761.398438,85663.585938,85544.445312,85537.562500,85406.531250,85446.968750,85436.968750</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:27:10</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>24</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>83858.109375,83777.750000,83749.859375,83719.812500,83644.953125,83621.890625,83622.609375,83594.492188,83602.171875,83568.679688,83549.578125,83536.625000,83524.218750,83517.664062,83498.390625,83491.601562,83501.031250,83487.406250,83486.617188,83429.718750,83456.343750,83454.664062,83435.421875,83421.171875</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>83738.265625,83743.867188,83668.750000,83676.265625,83679.734375,83644.312500,83559.179688,83549.437500,83612.078125,83489.406250,83476.570312,83469.976562,83379.570312,83459.000000,83425.578125,83437.093750,83331.109375,83417.585938,83485.203125,83328.625000,83324.765625,83379.671875,83291.601562,83279.757812</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>83428.625000,83221.539062,83051.070312,82965.226562,82805.703125,82668.046875,82556.562500,82433.968750,82336.875000,82221.414062,82099.992188,82076.671875,82048.812500,81960.023438,81837.773438,81836.968750,81699.843750,81668.500000,81506.492188,81411.562500,81372.765625,81328.257812,81262.203125,81215.742188</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>83603.695312,83451.734375,83327.062500,83248.523438,83089.851562,83036.343750,82980.492188,82870.390625,82819.468750,82737.312500,82616.937500,82646.601562,82567.968750,82501.578125,82452.039062,82465.726562,82366.718750,82324.156250,82287.914062,82248.703125,82225.734375,82135.296875,82141.281250,82075.703125</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3001,6 +3001,44 @@
       </c>
       <c r="F68" t="n">
         <v>83421.171875</v>
+      </c>
+      <c r="G68" t="n">
+        <v>84168.5625</v>
+      </c>
+      <c r="H68" t="n">
+        <v>747.390625</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.887968860107359</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.7308128330072161</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:38:28</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>24</v>
+      </c>
+      <c r="F69" t="n">
+        <v>83792.03125</v>
       </c>
     </row>
   </sheetData>
@@ -3014,7 +3052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7137,6 +7175,24 @@
           <t>83858.109375,83777.750000,83749.859375,83719.812500,83644.953125,83621.890625,83622.609375,83594.492188,83602.171875,83568.679688,83549.578125,83536.625000,83524.218750,83517.664062,83498.390625,83491.601562,83501.031250,83487.406250,83486.617188,83429.718750,83456.343750,83454.664062,83435.421875,83421.171875</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>83962.328125,84095.609375,84503.460938,83615.250000,83241.976562,83499.351562,83461.343750,83578.937500,84236.421875,83641.148438,84392.218750,84466.500000,84095.507812,84453.281250,84388.710938,84359.976562,84332.062500,84263.421875,84385.460938,84570.992188,84595.710938,84199.531250,84216.000000,84168.562500</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>104.218750,317.859375,753.601562,104.562500,402.976562,122.539062,161.265625,15.554688,634.250000,72.468749,842.640625,929.875000,571.289062,935.617188,890.320312,868.375001,831.031250,776.015625,898.843749,1141.273438,1139.367188,744.867188,780.578125,747.390625</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>0.124126,0.377974,0.891800,0.125052,0.484103,0.146755,0.193222,0.018611,0.752940,0.086642,0.998481,1.100880,0.679334,1.107852,1.055023,1.029368,0.985427,0.920940,1.065164,1.349486,1.346838,0.884645,0.926876,0.887969</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>0.7308128330072161</v>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
           <t>83738.265625,83743.867188,83668.750000,83676.265625,83679.734375,83644.312500,83559.179688,83549.437500,83612.078125,83489.406250,83476.570312,83469.976562,83379.570312,83459.000000,83425.578125,83437.093750,83331.109375,83417.585938,83485.203125,83328.625000,83324.765625,83379.671875,83291.601562,83279.757812</t>
@@ -7150,6 +7206,49 @@
       <c r="M68" t="inlineStr">
         <is>
           <t>83603.695312,83451.734375,83327.062500,83248.523438,83089.851562,83036.343750,82980.492188,82870.390625,82819.468750,82737.312500,82616.937500,82646.601562,82567.968750,82501.578125,82452.039062,82465.726562,82366.718750,82324.156250,82287.914062,82248.703125,82225.734375,82135.296875,82141.281250,82075.703125</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:38:28</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>24</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>84163.835938,84124.906250,84114.484375,84113.101562,84072.023438,84047.406250,84028.406250,83990.445312,83980.507812,83927.140625,83911.960938,83893.140625,83914.640625,83816.695312,83788.796875,83812.757812,83804.742188,83754.882812,83787.625000,83752.968750,83721.906250,83725.242188,83755.937500,83792.031250</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>84086.296875,84090.328125,84090.875000,84047.062500,84013.343750,84077.109375,83909.476562,83987.132812,83941.687500,83857.812500,83805.609375,83721.765625,83700.531250,83669.585938,83630.468750,83677.085938,83519.976562,83608.609375,83737.125000,83533.500000,83539.218750,83622.875000,83584.765625,83599.796875</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>83804.265625,83670.148438,83520.335938,83469.484375,83335.968750,83195.523438,83082.093750,82949.921875,82850.375000,82702.875000,82607.593750,82534.703125,82558.203125,82319.171875,82214.929688,82190.078125,82109.812500,82025.476562,81933.945312,81839.484375,81763.031250,81668.015625,81709.750000,81721.367188</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>83973.335938,83861.015625,83782.539062,83730.031250,83615.359375,83544.906250,83459.382812,83360.679688,83328.007812,83202.820312,83119.156250,83083.515625,83065.156250,82871.156250,82828.773438,82834.859375,82771.945312,82698.687500,82681.171875,82651.234375,82587.187500,82493.085938,82574.750000,82564.406250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3039,6 +3039,44 @@
       </c>
       <c r="F69" t="n">
         <v>83792.03125</v>
+      </c>
+      <c r="G69" t="n">
+        <v>83930.5703125</v>
+      </c>
+      <c r="H69" t="n">
+        <v>138.5390625</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.1650638879066058</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.2669307260059805</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-26 04:42:20</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>24</v>
+      </c>
+      <c r="F70" t="n">
+        <v>84027.09375</v>
       </c>
     </row>
   </sheetData>
@@ -3052,7 +3090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7236,6 +7274,24 @@
           <t>84163.835938,84124.906250,84114.484375,84113.101562,84072.023438,84047.406250,84028.406250,83990.445312,83980.507812,83927.140625,83911.960938,83893.140625,83914.640625,83816.695312,83788.796875,83812.757812,83804.742188,83754.882812,83787.625000,83752.968750,83721.906250,83725.242188,83755.937500,83792.031250</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>84181.750000,84022.578125,84023.500000,84406.851562,84563.726562,84709.250000,84566.679688,84453.531250,83891.390625,84002.171875,83781.710938,83731.523438,83761.820312,83949.992188,84005.812500,83867.632812,83787.062500,84063.328125,84093.132812,83904.796875,84072.828125,83999.757812,83931.179688,83930.570312</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>17.914062,102.328125,90.984375,293.750001,491.703124,661.843750,538.273438,463.085938,89.117187,75.031250,130.250001,161.617188,152.820312,133.296876,217.015625,54.875001,17.679688,308.445313,305.507812,151.828125,350.921875,274.515624,175.242188,138.539062</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>0.021280,0.121786,0.108284,0.348017,0.581459,0.781312,0.636508,0.548332,0.106229,0.089321,0.155464,0.193018,0.182446,0.158781,0.258334,0.065430,0.021101,0.366920,0.363297,0.180953,0.417402,0.326805,0.208793,0.165064</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0.2669307260059805</v>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>84086.296875,84090.328125,84090.875000,84047.062500,84013.343750,84077.109375,83909.476562,83987.132812,83941.687500,83857.812500,83805.609375,83721.765625,83700.531250,83669.585938,83630.468750,83677.085938,83519.976562,83608.609375,83737.125000,83533.500000,83539.218750,83622.875000,83584.765625,83599.796875</t>
@@ -7249,6 +7305,49 @@
       <c r="M69" t="inlineStr">
         <is>
           <t>83973.335938,83861.015625,83782.539062,83730.031250,83615.359375,83544.906250,83459.382812,83360.679688,83328.007812,83202.820312,83119.156250,83083.515625,83065.156250,82871.156250,82828.773438,82834.859375,82771.945312,82698.687500,82681.171875,82651.234375,82587.187500,82493.085938,82574.750000,82564.406250</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-26 04:42:20</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>24</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>84005.117188,83962.765625,83960.289062,83948.812500,83937.007812,83963.859375,83977.609375,83952.273438,83982.273438,84011.515625,84019.085938,84044.289062,84063.531250,84026.398438,84039.929688,84061.406250,84080.953125,84048.093750,84043.375000,84067.703125,84040.804688,84019.031250,84016.664062,84027.093750</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>84002.476562,84014.179688,83915.132812,83888.890625,83960.000000,84052.953125,83976.289062,83960.468750,84008.000000,83992.156250,83989.062500,83944.000000,83979.882812,83997.742188,83973.953125,84012.250000,83980.914062,84012.093750,84064.812500,83929.117188,83935.882812,83938.640625,83983.437500,83945.406250</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>83756.156250,83670.953125,83584.453125,83558.757812,83451.687500,83366.906250,83366.429688,83257.312500,83191.984375,83145.125000,83080.414062,83080.328125,83062.203125,82904.609375,82834.875000,82778.796875,82776.187500,82672.031250,82557.601562,82562.359375,82487.437500,82405.078125,82413.312500,82374.882812</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>83889.500000,83796.789062,83752.335938,83714.492188,83635.101562,83633.437500,83590.976562,83507.632812,83530.101562,83480.726562,83438.226562,83467.125000,83423.171875,83324.054688,83333.859375,83304.937500,83284.632812,83206.367188,83184.781250,83219.468750,83160.343750,83054.359375,83087.070312,83073.937500</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3077,6 +3077,44 @@
       </c>
       <c r="F70" t="n">
         <v>84027.09375</v>
+      </c>
+      <c r="G70" t="n">
+        <v>84316.796875</v>
+      </c>
+      <c r="H70" t="n">
+        <v>289.703125</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.3435888645408175</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.1933179612457634</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-27 05:02:18</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>24</v>
+      </c>
+      <c r="F71" t="n">
+        <v>84231.296875</v>
       </c>
     </row>
   </sheetData>
@@ -3090,7 +3128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7335,6 +7373,24 @@
           <t>84005.117188,83962.765625,83960.289062,83948.812500,83937.007812,83963.859375,83977.609375,83952.273438,83982.273438,84011.515625,84019.085938,84044.289062,84063.531250,84026.398438,84039.929688,84061.406250,84080.953125,84048.093750,84043.375000,84067.703125,84040.804688,84019.031250,84016.664062,84027.093750</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>83918.351562,83882.648438,84103.921875,84194.906250,84004.796875,84171.546875,84161.007812,84053.781250,83931.867188,84014.562500,84146.859375,84104.296875,84126.640625,83994.609375,84000.250000,84016.328125,84137.617188,84266.359375,84421.437500,84291.210938,84471.476562,84435.343750,84375.312500,84316.796875</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>86.765626,80.117188,143.632813,246.093750,67.789063,207.687500,183.398438,101.507812,50.406251,3.046875,127.773437,60.007813,63.109375,31.789063,39.679688,45.078125,56.664062,218.265625,378.062500,223.507812,430.671874,416.312500,358.648438,289.703125</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>0.103393,0.095511,0.170780,0.292291,0.080697,0.246743,0.217914,0.120765,0.060056,0.003627,0.151846,0.071349,0.075017,0.037847,0.047238,0.053654,0.067347,0.259019,0.447828,0.265161,0.509843,0.493055,0.425063,0.343589</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0.1933179612457634</v>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>84002.476562,84014.179688,83915.132812,83888.890625,83960.000000,84052.953125,83976.289062,83960.468750,84008.000000,83992.156250,83989.062500,83944.000000,83979.882812,83997.742188,83973.953125,84012.250000,83980.914062,84012.093750,84064.812500,83929.117188,83935.882812,83938.640625,83983.437500,83945.406250</t>
@@ -7348,6 +7404,49 @@
       <c r="M70" t="inlineStr">
         <is>
           <t>83889.500000,83796.789062,83752.335938,83714.492188,83635.101562,83633.437500,83590.976562,83507.632812,83530.101562,83480.726562,83438.226562,83467.125000,83423.171875,83324.054688,83333.859375,83304.937500,83284.632812,83206.367188,83184.781250,83219.468750,83160.343750,83054.359375,83087.070312,83073.937500</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-27 05:02:18</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>24</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>84387.937500,84343.671875,84354.328125,84372.242188,84348.609375,84348.304688,84362.703125,84360.804688,84339.562500,84335.929688,84322.523438,84328.742188,84316.828125,84292.000000,84287.078125,84304.945312,84296.164062,84278.828125,84243.750000,84271.203125,84268.359375,84244.140625,84225.351562,84231.296875</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>84363.968750,84323.265625,84314.437500,84301.203125,84349.570312,84329.367188,84274.906250,84331.218750,84292.343750,84236.171875,84222.117188,84156.187500,84196.937500,84207.531250,84196.375000,84202.468750,84176.359375,84147.390625,84122.679688,84107.585938,84070.312500,84112.390625,84045.296875,84013.148438</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>84105.195312,84050.687500,83983.062500,84015.578125,83917.765625,83815.640625,83847.101562,83825.585938,83652.320312,83588.726562,83521.109375,83542.437500,83440.671875,83323.546875,83242.343750,83218.234375,83128.820312,83096.468750,82959.140625,82944.515625,82892.093750,82824.593750,82769.359375,82716.140625</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>84237.156250,84176.906250,84171.187500,84147.437500,84092.804688,84068.578125,84069.460938,84016.171875,83994.406250,83916.281250,83867.367188,83869.093750,83830.953125,83722.054688,83714.164062,83724.093750,83645.406250,83629.765625,83551.875000,83593.687500,83546.406250,83463.484375,83452.070312,83443.875000</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3115,6 +3115,44 @@
       </c>
       <c r="F71" t="n">
         <v>84231.296875</v>
+      </c>
+      <c r="G71" t="n">
+        <v>83389.4765625</v>
+      </c>
+      <c r="H71" t="n">
+        <v>841.8203125</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1.009504253056511</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.5029135779383859</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:04:02</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>24</v>
+      </c>
+      <c r="F72" t="n">
+        <v>83335.421875</v>
       </c>
     </row>
   </sheetData>
@@ -3128,7 +3166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7434,6 +7472,24 @@
           <t>84387.937500,84343.671875,84354.328125,84372.242188,84348.609375,84348.304688,84362.703125,84360.804688,84339.562500,84335.929688,84322.523438,84328.742188,84316.828125,84292.000000,84287.078125,84304.945312,84296.164062,84278.828125,84243.750000,84271.203125,84268.359375,84244.140625,84225.351562,84231.296875</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>84506.523438,84773.257812,84775.679688,84942.039062,84872.648438,84877.023438,84783.882812,85029.343750,84520.000000,84449.476562,84409.671875,84559.742188,84798.726562,84717.820312,84532.203125,84664.531250,84187.882812,84462.132812,84125.796875,83686.726562,83405.000000,83325.156250,83482.468750,83389.476562</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>118.585938,429.585938,421.351562,569.796874,524.039062,528.718749,421.179688,668.539062,180.437500,113.546874,87.148437,230.999999,481.898438,425.820312,245.125000,359.585938,108.281249,183.304688,117.953125,584.476562,863.359375,918.984375,742.882812,841.820312</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>0.140328,0.506747,0.497019,0.670807,0.617442,0.622923,0.496769,0.786245,0.213485,0.134455,0.103245,0.273180,0.568285,0.502634,0.289978,0.424719,0.128619,0.217026,0.140210,0.698410,1.035141,1.102889,0.889867,1.009504</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0.5029135779383859</v>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>84363.968750,84323.265625,84314.437500,84301.203125,84349.570312,84329.367188,84274.906250,84331.218750,84292.343750,84236.171875,84222.117188,84156.187500,84196.937500,84207.531250,84196.375000,84202.468750,84176.359375,84147.390625,84122.679688,84107.585938,84070.312500,84112.390625,84045.296875,84013.148438</t>
@@ -7447,6 +7503,49 @@
       <c r="M71" t="inlineStr">
         <is>
           <t>84237.156250,84176.906250,84171.187500,84147.437500,84092.804688,84068.578125,84069.460938,84016.171875,83994.406250,83916.281250,83867.367188,83869.093750,83830.953125,83722.054688,83714.164062,83724.093750,83645.406250,83629.765625,83551.875000,83593.687500,83546.406250,83463.484375,83452.070312,83443.875000</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:04:02</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>24</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>83436.937500,83350.070312,83312.187500,83293.968750,83265.773438,83245.554688,83244.640625,83222.296875,83204.617188,83206.539062,83196.578125,83216.695312,83238.632812,83237.250000,83243.515625,83263.757812,83275.593750,83288.320312,83274.750000,83286.140625,83314.601562,83311.484375,83308.507812,83335.421875</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>83440.164062,83388.125000,83328.265625,83259.523438,83276.390625,83303.992188,83226.304688,83185.125000,83235.984375,83202.718750,83235.421875,83190.539062,83120.078125,83224.890625,83204.500000,83272.882812,83314.273438,83191.765625,83314.625000,83256.093750,83294.390625,83275.320312,83296.835938,83283.875000</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>83109.835938,82982.570312,82864.695312,82830.195312,82728.453125,82600.281250,82635.960938,82571.992188,82404.757812,82313.109375,82253.117188,82282.304688,82255.234375,82169.679688,82146.265625,82123.453125,82061.453125,82044.781250,81955.171875,81921.140625,81928.773438,81878.359375,81857.578125,81844.460938</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>83237.500000,83104.898438,83043.609375,82972.984375,82898.351562,82858.585938,82843.914062,82759.601562,82743.101562,82638.437500,82612.093750,82637.070312,82622.156250,82563.132812,82597.437500,82611.460938,82550.750000,82535.789062,82527.093750,82540.468750,82532.585938,82477.250000,82478.125000,82453.414062</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3153,6 +3153,44 @@
       </c>
       <c r="F72" t="n">
         <v>83335.421875</v>
+      </c>
+      <c r="G72" t="n">
+        <v>83281.3203125</v>
+      </c>
+      <c r="H72" t="n">
+        <v>54.1015625</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.06496242170152014</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.3718655674532553</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:28:47</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>24</v>
+      </c>
+      <c r="F73" t="n">
+        <v>83520.90625</v>
       </c>
     </row>
   </sheetData>
@@ -3166,7 +3204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7533,6 +7571,24 @@
           <t>83436.937500,83350.070312,83312.187500,83293.968750,83265.773438,83245.554688,83244.640625,83222.296875,83204.617188,83206.539062,83196.578125,83216.695312,83238.632812,83237.250000,83243.515625,83263.757812,83275.593750,83288.320312,83274.750000,83286.140625,83314.601562,83311.484375,83308.507812,83335.421875</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>83134.007812,82912.039062,82913.578125,82624.179688,82908.132812,83058.929688,83539.023438,83629.890625,82988.632812,83365.789062,83677.390625,83846.953125,84017.421875,83364.843750,83501.476562,83181.031250,83513.289062,83456.742188,83146.476562,83024.781250,82930.046875,83038.382812,83170.562500,83281.320312</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>302.929688,438.031249,398.609375,669.789062,357.640626,186.625001,294.382812,407.593750,215.984376,159.250001,480.812500,630.257813,778.789063,127.593750,257.960938,82.726562,237.695312,168.421876,128.273438,261.359375,384.554687,273.101562,137.945312,54.101562</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>0.364387,0.528308,0.480753,0.810645,0.431370,0.224690,0.352390,0.487378,0.260258,0.191026,0.574603,0.751676,0.926938,0.153055,0.308930,0.099454,0.284620,0.201807,0.154274,0.314797,0.463710,0.328886,0.165858,0.064962</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>0.3718655674532553</v>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>83440.164062,83388.125000,83328.265625,83259.523438,83276.390625,83303.992188,83226.304688,83185.125000,83235.984375,83202.718750,83235.421875,83190.539062,83120.078125,83224.890625,83204.500000,83272.882812,83314.273438,83191.765625,83314.625000,83256.093750,83294.390625,83275.320312,83296.835938,83283.875000</t>
@@ -7546,6 +7602,49 @@
       <c r="M72" t="inlineStr">
         <is>
           <t>83237.500000,83104.898438,83043.609375,82972.984375,82898.351562,82858.585938,82843.914062,82759.601562,82743.101562,82638.437500,82612.093750,82637.070312,82622.156250,82563.132812,82597.437500,82611.460938,82550.750000,82535.789062,82527.093750,82540.468750,82532.585938,82477.250000,82478.125000,82453.414062</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:28:47</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>24</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>83291.226562,83285.593750,83284.289062,83306.851562,83335.968750,83351.882812,83361.242188,83395.703125,83390.171875,83388.562500,83386.304688,83410.554688,83427.359375,83436.640625,83449.812500,83470.890625,83465.445312,83447.578125,83464.085938,83458.765625,83466.039062,83467.835938,83473.039062,83520.906250</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>83302.101562,83361.984375,83244.875000,83327.437500,83384.531250,83394.132812,83388.375000,83426.781250,83437.703125,83461.718750,83439.593750,83427.203125,83435.070312,83508.187500,83468.609375,83491.093750,83468.156250,83466.328125,83520.203125,83451.585938,83491.093750,83414.382812,83568.898438,83506.148438</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>82911.226562,82842.289062,82768.718750,82778.515625,82729.539062,82671.617188,82722.921875,82708.093750,82620.546875,82552.906250,82527.453125,82527.640625,82492.523438,82444.492188,82436.523438,82396.781250,82363.578125,82340.156250,82218.500000,82166.156250,82187.335938,82153.406250,82116.343750,82148.492188</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>83092.476562,83005.476562,82966.617188,82961.078125,82957.695312,82938.812500,82958.718750,82945.578125,82951.679688,82875.515625,82823.375000,82859.000000,82854.937500,82788.554688,82835.953125,82820.750000,82777.953125,82740.757812,82715.945312,82736.000000,82718.046875,82651.156250,82668.640625,82694.523438</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3191,6 +3191,44 @@
       </c>
       <c r="F73" t="n">
         <v>83520.90625</v>
+      </c>
+      <c r="G73" t="n">
+        <v>83158.0078125</v>
+      </c>
+      <c r="H73" t="n">
+        <v>362.8984375</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.4363962618227255</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.4668039234956356</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-30 05:16:26</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>24</v>
+      </c>
+      <c r="F74" t="n">
+        <v>83143.453125</v>
       </c>
     </row>
   </sheetData>
@@ -3204,7 +3242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7632,6 +7670,24 @@
           <t>83291.226562,83285.593750,83284.289062,83306.851562,83335.968750,83351.882812,83361.242188,83395.703125,83390.171875,83388.562500,83386.304688,83410.554688,83427.359375,83436.640625,83449.812500,83470.890625,83465.445312,83447.578125,83464.085938,83458.765625,83466.039062,83467.835938,83473.039062,83520.906250</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>83976.007812,83948.132812,83845.921875,84221.328125,84000.906250,84324.031250,84309.210938,84186.218750,83717.421875,83041.390625,83034.929688,83055.421875,83609.976562,83549.007812,83582.671875,83473.882812,83578.828125,83638.406250,83418.281250,83404.773438,83347.671875,83269.156250,83174.046875,83158.007812</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>684.781251,662.539062,561.632813,914.476563,664.937500,972.148438,947.968749,790.515625,327.250000,347.171875,351.375001,355.132813,182.617188,112.367188,132.859375,2.992188,113.382813,190.828125,45.804688,53.992188,118.367187,198.679688,298.992187,362.898438</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>0.815449,0.789224,0.669839,1.085802,0.791584,1.152872,1.124395,0.939008,0.390898,0.418071,0.423165,0.427585,0.218416,0.134493,0.158956,0.003585,0.135660,0.228158,0.054910,0.064735,0.142016,0.238599,0.359478,0.436396</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0.4668039234956356</v>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>83302.101562,83361.984375,83244.875000,83327.437500,83384.531250,83394.132812,83388.375000,83426.781250,83437.703125,83461.718750,83439.593750,83427.203125,83435.070312,83508.187500,83468.609375,83491.093750,83468.156250,83466.328125,83520.203125,83451.585938,83491.093750,83414.382812,83568.898438,83506.148438</t>
@@ -7645,6 +7701,49 @@
       <c r="M73" t="inlineStr">
         <is>
           <t>83092.476562,83005.476562,82966.617188,82961.078125,82957.695312,82938.812500,82958.718750,82945.578125,82951.679688,82875.515625,82823.375000,82859.000000,82854.937500,82788.554688,82835.953125,82820.750000,82777.953125,82740.757812,82715.945312,82736.000000,82718.046875,82651.156250,82668.640625,82694.523438</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-30 05:16:26</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>24</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>83175.976562,83160.375000,83135.484375,83144.390625,83146.218750,83136.812500,83134.875000,83131.984375,83115.039062,83120.226562,83090.921875,83112.921875,83127.328125,83117.468750,83133.796875,83155.781250,83145.851562,83120.773438,83151.046875,83163.328125,83144.789062,83129.125000,83113.992188,83143.453125</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>83182.312500,83279.960938,83126.351562,83120.085938,83176.718750,83157.015625,83201.054688,83139.726562,83146.851562,83128.789062,83146.250000,83098.125000,83132.968750,83155.875000,83177.382812,83145.578125,83138.968750,83163.789062,83227.281250,83125.843750,83163.726562,83078.703125,83171.265625,83125.914062</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>82850.968750,82796.703125,82709.195312,82709.265625,82624.500000,82562.476562,82560.812500,82502.757812,82412.570312,82357.046875,82281.000000,82283.953125,82246.851562,82205.078125,82199.859375,82142.398438,82118.390625,82080.656250,81982.242188,82001.953125,81975.507812,81930.703125,81893.031250,81908.343750</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>83006.851562,82932.765625,82857.062500,82852.210938,82809.343750,82774.187500,82764.140625,82732.023438,82708.460938,82653.937500,82581.648438,82595.328125,82597.140625,82548.265625,82581.765625,82553.515625,82522.984375,82454.609375,82461.734375,82485.515625,82456.109375,82377.218750,82381.390625,82404.664062</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3229,6 +3229,44 @@
       </c>
       <c r="F74" t="n">
         <v>83143.453125</v>
+      </c>
+      <c r="G74" t="n">
+        <v>84234.140625</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1090.6875</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1.294828310596301</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.8062676107492805</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-10-01 05:31:32</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>24</v>
+      </c>
+      <c r="F75" t="n">
+        <v>83947.640625</v>
       </c>
     </row>
   </sheetData>
@@ -3242,7 +3280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7731,6 +7769,24 @@
           <t>83175.976562,83160.375000,83135.484375,83144.390625,83146.218750,83136.812500,83134.875000,83131.984375,83115.039062,83120.226562,83090.921875,83112.921875,83127.328125,83117.468750,83133.796875,83155.781250,83145.851562,83120.773438,83151.046875,83163.328125,83144.789062,83129.125000,83113.992188,83143.453125</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>83005.882812,83271.382812,83023.148438,83598.187500,83883.359375,83879.007812,85258.070312,84579.820312,83754.468750,84078.968750,84299.851562,84007.812500,83911.906250,83558.976562,83617.757812,83712.593750,83625.148438,83556.148438,83455.890625,83459.609375,83444.132812,83695.539062,84049.593750,84234.140625</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>170.093749,111.007812,112.335938,453.796875,737.140625,742.195312,2123.195312,1447.835938,639.429688,958.742188,1208.929688,894.890625,784.578125,441.507812,483.960938,556.812500,479.296876,435.374999,304.843750,296.281250,299.343751,566.414062,935.601562,1090.687500</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>0.204918,0.133308,0.135307,0.542831,0.878769,0.884840,2.490316,1.711798,0.763457,1.140288,1.434083,1.065247,0.935002,0.528379,0.578778,0.665148,0.573149,0.521057,0.365275,0.355000,0.358736,0.676755,1.113154,1.294828</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0.8062676107492805</v>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>83182.312500,83279.960938,83126.351562,83120.085938,83176.718750,83157.015625,83201.054688,83139.726562,83146.851562,83128.789062,83146.250000,83098.125000,83132.968750,83155.875000,83177.382812,83145.578125,83138.968750,83163.789062,83227.281250,83125.843750,83163.726562,83078.703125,83171.265625,83125.914062</t>
@@ -7744,6 +7800,49 @@
       <c r="M74" t="inlineStr">
         <is>
           <t>83006.851562,82932.765625,82857.062500,82852.210938,82809.343750,82774.187500,82764.140625,82732.023438,82708.460938,82653.937500,82581.648438,82595.328125,82597.140625,82548.265625,82581.765625,82553.515625,82522.984375,82454.609375,82461.734375,82485.515625,82456.109375,82377.218750,82381.390625,82404.664062</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-10-01 05:31:32</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>24</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>84239.289062,84232.875000,84191.453125,84199.843750,84176.453125,84154.515625,84144.468750,84108.015625,84082.445312,84066.625000,84029.820312,84021.750000,83995.226562,83966.953125,83983.835938,83988.250000,83983.718750,83964.500000,83974.765625,83973.585938,83958.171875,83936.093750,83925.078125,83947.640625</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>84240.578125,84293.812500,84172.601562,84186.804688,84207.031250,84105.734375,84160.187500,84092.007812,84093.843750,84024.015625,84030.273438,83965.101562,83933.781250,83975.203125,83946.335938,83930.500000,83953.515625,83935.171875,83979.664062,83944.078125,83909.187500,83878.484375,83910.554688,83909.304688</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>83731.296875,83637.132812,83503.210938,83495.414062,83382.070312,83322.789062,83300.398438,83209.375000,83109.718750,83060.734375,82974.359375,82955.265625,82899.265625,82856.945312,82839.757812,82785.140625,82761.406250,82752.156250,82644.867188,82625.679688,82610.781250,82595.117188,82570.109375,82575.656250</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>83970.882812,83875.250000,83758.796875,83763.101562,83679.023438,83612.734375,83596.671875,83529.164062,83517.359375,83449.796875,83372.554688,83345.007812,83335.781250,83274.375000,83282.937500,83268.359375,83242.796875,83205.601562,83183.632812,83194.921875,83166.812500,83101.882812,83104.953125,83136.203125</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3267,6 +3267,44 @@
       </c>
       <c r="F75" t="n">
         <v>83947.640625</v>
+      </c>
+      <c r="G75" t="n">
+        <v>86474.953125</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2527.3125</v>
+      </c>
+      <c r="I75" t="n">
+        <v>2.922594819272994</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.897601667416742</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-10-02 05:19:08</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>24</v>
+      </c>
+      <c r="F76" t="n">
+        <v>85975.703125</v>
       </c>
     </row>
   </sheetData>
@@ -3280,7 +3318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7830,6 +7868,24 @@
           <t>84239.289062,84232.875000,84191.453125,84199.843750,84176.453125,84154.515625,84144.468750,84108.015625,84082.445312,84066.625000,84029.820312,84021.750000,83995.226562,83966.953125,83983.835938,83988.250000,83983.718750,83964.500000,83974.765625,83973.585938,83958.171875,83936.093750,83925.078125,83947.640625</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>84076.257812,83371.843750,83519.460938,83744.476562,83922.062500,83882.023438,83706.460938,83925.406250,84022.726562,84130.062500,84164.703125,84872.046875,84767.851562,84644.929688,84607.078125,84529.218750,84719.218750,84848.726562,84762.750000,84883.750000,85165.742188,85485.812500,86641.687500,86474.953125</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>163.031249,861.031250,671.992188,455.367188,254.390625,272.492188,438.007812,182.609375,59.718749,63.437500,134.882813,850.296875,772.625001,677.976562,623.242187,540.968750,735.500000,884.226562,787.984375,910.164062,1207.570312,1549.718750,2716.609375,2527.312500</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>0.193909,1.032760,0.804594,0.543758,0.303127,0.324852,0.523266,0.217585,0.071075,0.075404,0.160261,1.001857,0.911460,0.800965,0.736631,0.639978,0.868162,1.042121,0.929635,1.072248,1.417906,1.812837,3.135453,2.922595</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>0.897601667416742</v>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
           <t>84240.578125,84293.812500,84172.601562,84186.804688,84207.031250,84105.734375,84160.187500,84092.007812,84093.843750,84024.015625,84030.273438,83965.101562,83933.781250,83975.203125,83946.335938,83930.500000,83953.515625,83935.171875,83979.664062,83944.078125,83909.187500,83878.484375,83910.554688,83909.304688</t>
@@ -7843,6 +7899,49 @@
       <c r="M75" t="inlineStr">
         <is>
           <t>83970.882812,83875.250000,83758.796875,83763.101562,83679.023438,83612.734375,83596.671875,83529.164062,83517.359375,83449.796875,83372.554688,83345.007812,83335.781250,83274.375000,83282.937500,83268.359375,83242.796875,83205.601562,83183.632812,83194.921875,83166.812500,83101.882812,83104.953125,83136.203125</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-10-02 05:19:08</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>24</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>86349.296875,86348.765625,86351.507812,86354.828125,86337.812500,86306.265625,86298.914062,86241.242188,86229.593750,86201.078125,86216.703125,86157.054688,86141.109375,86072.421875,86097.171875,86033.093750,86062.398438,86046.585938,85988.312500,85995.718750,85971.710938,85955.531250,85967.687500,85975.703125</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>86335.625000,86329.195312,86363.335938,86367.718750,86256.539062,86231.046875,86249.515625,86273.179688,86144.328125,86182.562500,86172.257812,86069.078125,86012.484375,86050.140625,85981.015625,86014.132812,86008.539062,85892.351562,85971.984375,85963.859375,85914.882812,85896.406250,85921.617188,85886.234375</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>85688.593750,85581.773438,85462.000000,85404.195312,85269.679688,85152.273438,85055.062500,84932.554688,84864.250000,84754.671875,84727.937500,84586.781250,84596.375000,84450.421875,84402.812500,84330.078125,84334.125000,84325.921875,84110.992188,84079.609375,84042.437500,83997.703125,83976.960938,83957.171875</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>85987.132812,85894.437500,85813.906250,85794.625000,85685.125000,85575.000000,85535.765625,85412.945312,85435.164062,85340.406250,85311.960938,85208.914062,85190.281250,85051.078125,85047.093750,85012.585938,85040.781250,84991.375000,84856.875000,84858.796875,84790.906250,84728.468750,84723.312500,84761.484375</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3305,6 +3305,44 @@
       </c>
       <c r="F76" t="n">
         <v>85975.703125</v>
+      </c>
+      <c r="G76" t="n">
+        <v>84539.0078125</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1436.6953125</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1.699446621950499</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1.17047921071878</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:01:58</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>24</v>
+      </c>
+      <c r="F77" t="n">
+        <v>84346.078125</v>
       </c>
     </row>
   </sheetData>
@@ -3318,7 +3356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7929,6 +7967,24 @@
           <t>86349.296875,86348.765625,86351.507812,86354.828125,86337.812500,86306.265625,86298.914062,86241.242188,86229.593750,86201.078125,86216.703125,86157.054688,86141.109375,86072.421875,86097.171875,86033.093750,86062.398438,86046.585938,85988.312500,85995.718750,85971.710938,85955.531250,85967.687500,85975.703125</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>85964.367188,86088.507812,86235.648438,86352.273438,86281.000000,86412.210938,86811.281250,86579.007812,85671.828125,85316.351562,85143.500000,84776.093750,84240.843750,84291.492188,84430.546875,84512.601562,84549.578125,84504.882812,84638.718750,84628.148438,84585.031250,84681.000000,84573.843750,84539.007812</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>384.929688,260.257812,115.859374,2.554688,56.812500,105.945312,512.367188,337.765624,557.765625,884.726562,1073.203125,1380.960938,1900.265625,1780.929688,1666.625000,1520.492188,1512.820313,1541.703126,1349.593750,1367.570312,1386.679688,1274.531250,1393.843750,1436.695312</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>0.447778,0.302314,0.134352,0.002958,0.065846,0.122605,0.590208,0.390124,0.651049,1.036995,1.260464,1.628951,2.255753,2.112823,1.973960,1.799131,1.789270,1.824395,1.594535,1.615976,1.639391,1.505097,1.648079,1.699447</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>1.17047921071878</v>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>86335.625000,86329.195312,86363.335938,86367.718750,86256.539062,86231.046875,86249.515625,86273.179688,86144.328125,86182.562500,86172.257812,86069.078125,86012.484375,86050.140625,85981.015625,86014.132812,86008.539062,85892.351562,85971.984375,85963.859375,85914.882812,85896.406250,85921.617188,85886.234375</t>
@@ -7942,6 +7998,49 @@
       <c r="M76" t="inlineStr">
         <is>
           <t>85987.132812,85894.437500,85813.906250,85794.625000,85685.125000,85575.000000,85535.765625,85412.945312,85435.164062,85340.406250,85311.960938,85208.914062,85190.281250,85051.078125,85047.093750,85012.585938,85040.781250,84991.375000,84856.875000,84858.796875,84790.906250,84728.468750,84723.312500,84761.484375</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:01:58</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>24</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>84577.265625,84555.773438,84553.125000,84540.203125,84511.312500,84501.968750,84495.890625,84458.031250,84455.992188,84438.632812,84420.593750,84391.726562,84374.421875,84344.421875,84373.718750,84344.945312,84369.015625,84374.671875,84360.921875,84359.796875,84349.906250,84336.218750,84320.812500,84346.078125</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>84537.960938,84528.953125,84582.921875,84530.460938,84491.531250,84548.640625,84504.109375,84443.960938,84381.109375,84419.867188,84404.015625,84389.390625,84352.890625,84364.890625,84308.296875,84320.070312,84348.937500,84307.742188,84372.640625,84373.804688,84329.562500,84280.437500,84344.781250,84348.859375</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>84128.015625,84067.023438,83987.960938,83952.343750,83855.703125,83787.421875,83723.125000,83639.820312,83590.257812,83503.445312,83425.171875,83356.414062,83289.375000,83210.648438,83160.468750,83131.312500,83121.656250,83130.367188,83001.078125,82940.984375,82927.453125,82878.179688,82851.984375,82857.578125</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>84331.828125,84273.343750,84222.640625,84199.367188,84118.453125,84055.242188,84035.171875,83947.796875,83985.039062,83912.039062,83819.906250,83781.648438,83733.484375,83642.390625,83651.117188,83644.781250,83646.867188,83639.242188,83586.367188,83566.375000,83523.945312,83458.656250,83434.796875,83473.671875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3343,6 +3343,44 @@
       </c>
       <c r="F77" t="n">
         <v>84346.078125</v>
+      </c>
+      <c r="G77" t="n">
+        <v>84854.546875</v>
+      </c>
+      <c r="H77" t="n">
+        <v>508.46875</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.59922392933054</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.4080416216405293</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-04 05:34:20</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>24</v>
+      </c>
+      <c r="F78" t="n">
+        <v>84917.78125</v>
       </c>
     </row>
   </sheetData>
@@ -3356,7 +3394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8028,6 +8066,24 @@
           <t>84577.265625,84555.773438,84553.125000,84540.203125,84511.312500,84501.968750,84495.890625,84458.031250,84455.992188,84438.632812,84420.593750,84391.726562,84374.421875,84344.421875,84373.718750,84344.945312,84369.015625,84374.671875,84360.921875,84359.796875,84349.906250,84336.218750,84320.812500,84346.078125</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>84554.062500,84552.148438,84593.101562,84583.320312,84621.062500,84661.851562,84864.773438,84857.437500,84842.992188,84862.156250,84853.132812,84990.968750,84933.648438,84836.992188,84739.203125,84708.570312,84755.937500,84742.218750,84786.468750,84794.476562,84790.046875,84824.359375,84805.007812,84854.546875</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>23.203125,3.625001,39.976562,43.117188,109.750000,159.882812,368.882812,399.406250,386.999999,423.523438,432.539062,599.242188,559.226562,492.570312,365.484375,363.625001,386.921875,367.546875,425.546875,434.679688,440.140625,488.140625,484.195312,508.468750</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>0.027442,0.004287,0.047257,0.050976,0.129696,0.188849,0.434671,0.470679,0.456137,0.499072,0.509750,0.705066,0.658428,0.580608,0.431305,0.429266,0.456513,0.433723,0.501904,0.512627,0.519095,0.575472,0.570951,0.599224</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0.4080416216405293</v>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>84537.960938,84528.953125,84582.921875,84530.460938,84491.531250,84548.640625,84504.109375,84443.960938,84381.109375,84419.867188,84404.015625,84389.390625,84352.890625,84364.890625,84308.296875,84320.070312,84348.937500,84307.742188,84372.640625,84373.804688,84329.562500,84280.437500,84344.781250,84348.859375</t>
@@ -8041,6 +8097,49 @@
       <c r="M77" t="inlineStr">
         <is>
           <t>84331.828125,84273.343750,84222.640625,84199.367188,84118.453125,84055.242188,84035.171875,83947.796875,83985.039062,83912.039062,83819.906250,83781.648438,83733.484375,83642.390625,83651.117188,83644.781250,83646.867188,83639.242188,83586.367188,83566.375000,83523.945312,83458.656250,83434.796875,83473.671875</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-04 05:34:20</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>24</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>84853.546875,84847.468750,84856.265625,84884.125000,84880.765625,84901.734375,84893.531250,84874.945312,84889.734375,84891.828125,84895.187500,84897.039062,84889.578125,84870.867188,84898.289062,84893.726562,84901.148438,84877.234375,84894.437500,84902.750000,84910.835938,84899.781250,84903.093750,84917.781250</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>84849.171875,84870.335938,84855.273438,84856.171875,84881.828125,84929.343750,84903.890625,84882.484375,84842.250000,84829.867188,84889.281250,84848.921875,84876.054688,84877.640625,84843.656250,84851.437500,84856.132812,84813.687500,84880.710938,84845.234375,84862.523438,84846.046875,84892.054688,84890.031250</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>84607.921875,84589.398438,84550.546875,84596.468750,84524.890625,84512.000000,84476.984375,84399.828125,84369.781250,84334.898438,84277.210938,84251.523438,84164.640625,84167.312500,84137.031250,84083.250000,84052.515625,84024.765625,83918.257812,83894.156250,83900.015625,83865.187500,83824.812500,83835.218750</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>84734.406250,84698.843750,84673.218750,84706.960938,84660.078125,84647.015625,84636.062500,84592.914062,84619.289062,84578.812500,84514.304688,84517.914062,84507.062500,84434.429688,84459.414062,84454.625000,84428.148438,84379.156250,84361.414062,84369.351562,84349.531250,84296.117188,84281.085938,84304.398438</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3381,6 +3381,44 @@
       </c>
       <c r="F78" t="n">
         <v>84917.78125</v>
+      </c>
+      <c r="G78" t="n">
+        <v>85488.0234375</v>
+      </c>
+      <c r="H78" t="n">
+        <v>570.2421875</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.6670433641700725</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.8393590729819748</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-10-05 05:18:03</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>24</v>
+      </c>
+      <c r="F79" t="n">
+        <v>85040.7890625</v>
       </c>
     </row>
   </sheetData>
@@ -3394,7 +3432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8127,6 +8165,24 @@
           <t>84853.546875,84847.468750,84856.265625,84884.125000,84880.765625,84901.734375,84893.531250,84874.945312,84889.734375,84891.828125,84895.187500,84897.039062,84889.578125,84870.867188,84898.289062,84893.726562,84901.148438,84877.234375,84894.437500,84902.750000,84910.835938,84899.781250,84903.093750,84917.781250</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>85013.210938,85092.992188,85093.796875,85219.398438,85260.250000,85304.171875,85127.359375,85233.867188,85276.359375,85244.976562,85358.312500,85302.890625,85325.078125,85417.468750,85812.031250,85845.960938,86423.000000,86512.976562,86632.007812,86596.906250,86509.656250,86052.296875,85505.437500,85488.023438</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>159.664062,245.523438,237.531250,335.273438,379.484375,402.437500,233.828125,358.921876,386.625000,353.148438,463.125000,405.851563,435.500000,546.601562,913.742188,952.234376,1521.851562,1635.742188,1737.570312,1694.156250,1598.820312,1152.515625,602.343750,570.242188</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>0.187811,0.288535,0.279140,0.393424,0.445089,0.471768,0.274680,0.421102,0.453379,0.414275,0.542566,0.475777,0.510401,0.639918,1.064818,1.109236,1.760934,1.890748,2.005691,1.956370,1.848141,1.339320,0.704451,0.667043</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0.8393590729819748</v>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
           <t>84849.171875,84870.335938,84855.273438,84856.171875,84881.828125,84929.343750,84903.890625,84882.484375,84842.250000,84829.867188,84889.281250,84848.921875,84876.054688,84877.640625,84843.656250,84851.437500,84856.132812,84813.687500,84880.710938,84845.234375,84862.523438,84846.046875,84892.054688,84890.031250</t>
@@ -8140,6 +8196,49 @@
       <c r="M78" t="inlineStr">
         <is>
           <t>84734.406250,84698.843750,84673.218750,84706.960938,84660.078125,84647.015625,84636.062500,84592.914062,84619.289062,84578.812500,84514.304688,84517.914062,84507.062500,84434.429688,84459.414062,84454.625000,84428.148438,84379.156250,84361.414062,84369.351562,84349.531250,84296.117188,84281.085938,84304.398438</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-10-05 05:18:03</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>24</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>85428.187500,85363.500000,85344.023438,85336.210938,85268.335938,85256.289062,85244.109375,85211.296875,85201.640625,85194.156250,85176.968750,85191.921875,85146.906250,85120.453125,85135.054688,85149.734375,85162.078125,85127.132812,85133.476562,85111.007812,85120.421875,85086.671875,85040.617188,85040.789062</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>85364.671875,85342.359375,85284.820312,85278.484375,85245.164062,85205.734375,85154.953125,85138.375000,85085.195312,85190.242188,85138.656250,85053.414062,85027.703125,85082.898438,85036.007812,85044.890625,85058.250000,84960.929688,85021.351562,85006.546875,85023.296875,85048.585938,84957.328125,84957.500000</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>85010.007812,84893.875000,84768.976562,84706.304688,84544.929688,84470.554688,84359.031250,84265.382812,84197.101562,84116.468750,84020.078125,83993.843750,83930.218750,83894.929688,83841.921875,83835.453125,83856.835938,83797.039062,83696.328125,83629.156250,83632.656250,83603.367188,83540.023438,83546.750000</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>85209.671875,85084.625000,84998.656250,84953.656250,84822.593750,84737.414062,84689.437500,84610.062500,84601.585938,84528.187500,84427.007812,84426.976562,84391.171875,84330.500000,84324.078125,84358.859375,84383.031250,84307.000000,84289.921875,84248.351562,84246.046875,84159.664062,84133.468750,84128.718750</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3419,6 +3419,44 @@
       </c>
       <c r="F79" t="n">
         <v>85040.7890625</v>
+      </c>
+      <c r="G79" t="n">
+        <v>85496.5234375</v>
+      </c>
+      <c r="H79" t="n">
+        <v>455.734375</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.5330443352274467</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.7091748564904726</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02:12</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>24</v>
+      </c>
+      <c r="F80" t="n">
+        <v>85307.5625</v>
       </c>
     </row>
   </sheetData>
@@ -3432,7 +3470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8226,6 +8264,24 @@
           <t>85428.187500,85363.500000,85344.023438,85336.210938,85268.335938,85256.289062,85244.109375,85211.296875,85201.640625,85194.156250,85176.968750,85191.921875,85146.906250,85120.453125,85135.054688,85149.734375,85162.078125,85127.132812,85133.476562,85111.007812,85120.421875,85086.671875,85040.617188,85040.789062</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>86230.117188,86235.281250,86190.656250,85961.328125,86102.617188,86197.921875,85870.273438,86435.953125,85623.031250,85251.546875,85296.046875,85428.187500,85658.320312,85724.546875,85772.078125,85941.273438,85929.398438,85748.953125,85901.968750,85613.328125,85525.109375,85476.140625,85605.593750,85496.523438</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>801.929688,871.781250,846.632812,625.117187,834.281249,941.632813,626.164062,1224.656250,421.390625,57.390625,119.078125,236.265625,511.414062,604.093750,637.023437,791.539062,767.320312,621.820313,768.492188,502.320313,404.687500,389.468750,564.976562,455.734376</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>0.929988,1.010933,0.982279,0.727207,0.968938,1.092408,0.729198,1.416837,0.492146,0.067319,0.139606,0.276566,0.597040,0.704692,0.742693,0.921023,0.892966,0.725164,0.894615,0.586731,0.473180,0.455646,0.659976,0.533044</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>0.7091748564904726</v>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
           <t>85364.671875,85342.359375,85284.820312,85278.484375,85245.164062,85205.734375,85154.953125,85138.375000,85085.195312,85190.242188,85138.656250,85053.414062,85027.703125,85082.898438,85036.007812,85044.890625,85058.250000,84960.929688,85021.351562,85006.546875,85023.296875,85048.585938,84957.328125,84957.500000</t>
@@ -8239,6 +8295,49 @@
       <c r="M79" t="inlineStr">
         <is>
           <t>85209.671875,85084.625000,84998.656250,84953.656250,84822.593750,84737.414062,84689.437500,84610.062500,84601.585938,84528.187500,84427.007812,84426.976562,84391.171875,84330.500000,84324.078125,84358.859375,84383.031250,84307.000000,84289.921875,84248.351562,84246.046875,84159.664062,84133.468750,84128.718750</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02:12</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>24</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>85412.000000,85380.968750,85367.195312,85375.984375,85340.453125,85366.601562,85348.320312,85334.031250,85334.578125,85330.585938,85295.187500,85313.500000,85289.023438,85288.070312,85304.000000,85327.031250,85347.476562,85319.640625,85314.531250,85347.734375,85345.453125,85319.632812,85288.851562,85307.562500</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>85381.812500,85385.296875,85347.257812,85358.695312,85412.093750,85372.843750,85318.992188,85321.500000,85271.296875,85289.937500,85301.039062,85215.843750,85195.000000,85310.640625,85268.015625,85226.250000,85244.101562,85232.906250,85285.546875,85223.500000,85270.960938,85275.250000,85241.531250,85212.101562</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>85112.390625,85058.062500,84958.945312,84935.687500,84841.343750,84791.507812,84724.726562,84647.765625,84597.828125,84519.500000,84424.062500,84407.523438,84337.632812,84335.156250,84278.000000,84265.648438,84274.937500,84238.585938,84120.242188,84129.375000,84125.531250,84114.140625,84058.640625,84058.468750</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>85251.851562,85185.273438,85122.406250,85113.101562,85028.406250,84993.328125,84975.585938,84924.726562,84917.562500,84857.406250,84744.375000,84762.250000,84737.500000,84706.132812,84691.867188,84724.828125,84728.007812,84668.492188,84644.234375,84667.476562,84672.914062,84570.937500,84558.210938,84573.937500</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3457,6 +3457,44 @@
       </c>
       <c r="F80" t="n">
         <v>85307.5625</v>
+      </c>
+      <c r="G80" t="n">
+        <v>84174.3125</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1133.25</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1.346313342327566</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.7826310917947742</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-07 05:37:22</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>24</v>
+      </c>
+      <c r="F81" t="n">
+        <v>84172.328125</v>
       </c>
     </row>
   </sheetData>
@@ -3470,7 +3508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8325,6 +8363,24 @@
           <t>85412.000000,85380.968750,85367.195312,85375.984375,85340.453125,85366.601562,85348.320312,85334.031250,85334.578125,85330.585938,85295.187500,85313.500000,85289.023438,85288.070312,85304.000000,85327.031250,85347.476562,85319.640625,85314.531250,85347.734375,85345.453125,85319.632812,85288.851562,85307.562500</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>85539.531250,86003.570312,85971.851562,86139.953125,86236.187500,86193.757812,86306.929688,86600.023438,85710.000000,85576.093750,85719.367188,85494.000000,85610.000000,85607.578125,85614.656250,85527.218750,85547.773438,85535.492188,84391.421875,83847.562500,84122.523438,84075.812500,84174.312500,84174.312500</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>127.531250,622.601562,604.656251,763.968750,895.734375,827.156251,958.609376,1265.992188,375.421875,245.507812,424.179688,180.500000,320.976562,319.507813,310.656250,200.187500,200.296876,215.851562,923.109375,1500.171875,1222.929688,1243.820312,1114.539062,1133.250000</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>0.149090,0.723925,0.703319,0.886892,1.038699,0.959648,1.110698,1.461884,0.438014,0.286888,0.494847,0.211126,0.374929,0.373224,0.362854,0.234063,0.234135,0.252353,1.093843,1.789166,1.453748,1.479403,1.324085,1.346313</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0.7826310917947742</v>
+      </c>
       <c r="K80" t="inlineStr">
         <is>
           <t>85381.812500,85385.296875,85347.257812,85358.695312,85412.093750,85372.843750,85318.992188,85321.500000,85271.296875,85289.937500,85301.039062,85215.843750,85195.000000,85310.640625,85268.015625,85226.250000,85244.101562,85232.906250,85285.546875,85223.500000,85270.960938,85275.250000,85241.531250,85212.101562</t>
@@ -8338,6 +8394,49 @@
       <c r="M80" t="inlineStr">
         <is>
           <t>85251.851562,85185.273438,85122.406250,85113.101562,85028.406250,84993.328125,84975.585938,84924.726562,84917.562500,84857.406250,84744.375000,84762.250000,84737.500000,84706.132812,84691.867188,84724.828125,84728.007812,84668.492188,84644.234375,84667.476562,84672.914062,84570.937500,84558.210938,84573.937500</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-07 05:37:22</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>24</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>84160.187500,84160.460938,84167.359375,84187.851562,84176.750000,84196.609375,84191.515625,84177.515625,84171.367188,84160.609375,84146.687500,84154.656250,84148.843750,84159.414062,84171.078125,84172.453125,84180.351562,84183.273438,84179.062500,84188.710938,84199.921875,84192.437500,84167.796875,84172.328125</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>84112.906250,84221.226562,84164.578125,84224.585938,84219.773438,84244.515625,84206.304688,84189.164062,84165.703125,84167.648438,84152.617188,84151.640625,84137.359375,84223.671875,84186.195312,84131.000000,84141.171875,84168.671875,84197.046875,84126.398438,84163.789062,84130.515625,84151.093750,84153.539062</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>83650.617188,83584.742188,83518.421875,83507.851562,83419.921875,83372.968750,83345.718750,83273.914062,83215.953125,83147.929688,83082.156250,83046.039062,83006.062500,83010.984375,82977.171875,82916.304688,82908.632812,82871.851562,82724.343750,82707.679688,82720.710938,82720.000000,82690.781250,82651.132812</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>83869.070312,83799.218750,83737.000000,83753.726562,83705.054688,83670.312500,83656.343750,83621.687500,83600.640625,83551.875000,83462.164062,83478.078125,83457.804688,83440.132812,83445.281250,83425.640625,83392.546875,83352.046875,83329.984375,83334.054688,83343.226562,83281.523438,83281.429688,83272.890625</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3495,6 +3495,44 @@
       </c>
       <c r="F81" t="n">
         <v>84172.328125</v>
+      </c>
+      <c r="G81" t="n">
+        <v>82831.6875</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1340.640625</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1.618511786325734</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1.002764279807221</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-08 05:45:40</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>24</v>
+      </c>
+      <c r="F82" t="n">
+        <v>82556.21875</v>
       </c>
     </row>
   </sheetData>
@@ -3508,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8424,6 +8462,24 @@
           <t>84160.187500,84160.460938,84167.359375,84187.851562,84176.750000,84196.609375,84191.515625,84177.515625,84171.367188,84160.609375,84146.687500,84154.656250,84148.843750,84159.414062,84171.078125,84172.453125,84180.351562,84183.273438,84179.062500,84188.710938,84199.921875,84192.437500,84167.796875,84172.328125</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>84200.007812,84100.078125,83924.023438,83784.281250,83719.718750,83709.531250,83464.007812,83139.710938,82970.882812,83417.398438,83346.781250,83116.101562,83372.789062,83392.039062,83379.187500,83109.648438,83196.632812,83275.062500,83323.750000,83056.976562,83116.078125,82695.562500,82593.117188,82831.687500</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>39.820312,60.382813,243.335938,403.570312,457.031250,487.078125,727.507812,1037.804688,1200.484376,743.210938,799.906250,1038.554688,776.054688,767.374999,791.890625,1062.804688,983.718749,908.210938,855.312500,1131.734376,1083.843750,1496.875000,1574.679688,1340.640625</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>0.047293,0.071799,0.289948,0.481678,0.545906,0.581867,0.871643,1.248266,1.446874,0.890954,0.959733,1.249523,0.930825,0.920202,0.949746,1.278798,1.182402,1.090616,1.026493,1.362600,1.304012,1.810103,1.906551,1.618512</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>1.002764279807221</v>
+      </c>
       <c r="K81" t="inlineStr">
         <is>
           <t>84112.906250,84221.226562,84164.578125,84224.585938,84219.773438,84244.515625,84206.304688,84189.164062,84165.703125,84167.648438,84152.617188,84151.640625,84137.359375,84223.671875,84186.195312,84131.000000,84141.171875,84168.671875,84197.046875,84126.398438,84163.789062,84130.515625,84151.093750,84153.539062</t>
@@ -8437,6 +8493,49 @@
       <c r="M81" t="inlineStr">
         <is>
           <t>83869.070312,83799.218750,83737.000000,83753.726562,83705.054688,83670.312500,83656.343750,83621.687500,83600.640625,83551.875000,83462.164062,83478.078125,83457.804688,83440.132812,83445.281250,83425.640625,83392.546875,83352.046875,83329.984375,83334.054688,83343.226562,83281.523438,83281.429688,83272.890625</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-08 05:45:40</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>24</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>82760.812500,82774.312500,82773.593750,82775.664062,82768.187500,82776.234375,82747.437500,82738.109375,82685.281250,82690.867188,82657.742188,82688.734375,82660.359375,82677.265625,82668.601562,82665.968750,82622.382812,82611.281250,82636.414062,82619.242188,82625.484375,82603.453125,82563.171875,82556.218750</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>82739.414062,82845.328125,82772.171875,82837.679688,82848.117188,82830.281250,82806.570312,82693.445312,82736.140625,82735.539062,82754.906250,82734.226562,82742.070312,82764.078125,82723.062500,82669.687500,82679.632812,82742.734375,82753.203125,82642.859375,82668.640625,82614.406250,82614.773438,82607.718750</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>82373.640625,82326.609375,82243.023438,82202.687500,82127.156250,82082.625000,82065.054688,82030.359375,81891.187500,81826.843750,81750.429688,81775.921875,81708.867188,81741.218750,81706.859375,81620.437500,81588.265625,81514.593750,81402.359375,81361.781250,81328.125000,81294.125000,81269.250000,81197.609375</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>82557.343750,82487.570312,82436.070312,82410.023438,82379.859375,82342.046875,82286.562500,82285.609375,82236.085938,82165.375000,82081.210938,82118.765625,82086.992188,82104.468750,82116.078125,82053.593750,81991.492188,81889.562500,81921.375000,81901.460938,81897.828125,81770.273438,81783.906250,81767.515625</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3533,6 +3533,44 @@
       </c>
       <c r="F82" t="n">
         <v>82556.21875</v>
+      </c>
+      <c r="G82" t="n">
+        <v>82298.953125</v>
+      </c>
+      <c r="H82" t="n">
+        <v>257.265625</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.3125989034262093</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.8467914883468088</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-09 05:49:41</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>24</v>
+      </c>
+      <c r="F83" t="n">
+        <v>81996.171875</v>
       </c>
     </row>
   </sheetData>
@@ -3546,7 +3584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8523,6 +8561,24 @@
           <t>82760.812500,82774.312500,82773.593750,82775.664062,82768.187500,82776.234375,82747.437500,82738.109375,82685.281250,82690.867188,82657.742188,82688.734375,82660.359375,82677.265625,82668.601562,82665.968750,82622.382812,82611.281250,82636.414062,82619.242188,82625.484375,82603.453125,82563.171875,82556.218750</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>82813.601562,82938.671875,82811.968750,83059.867188,82662.000000,82429.117188,82249.437500,82112.101562,82638.890625,80989.343750,80888.109375,80679.742188,81436.046875,81704.578125,81750.789062,81626.039062,81833.296875,81692.789062,81734.703125,81912.062500,82056.156250,82360.210938,82174.703125,82298.953125</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>52.789062,164.359375,38.375000,284.203126,106.187500,347.117188,498.000000,626.007812,46.390625,1701.523438,1769.632813,2008.992188,1224.312500,972.687500,917.812499,1039.929688,789.085937,918.492188,901.710937,707.179688,569.328125,243.242188,388.468750,257.265625</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>0.063744,0.198170,0.046340,0.342167,0.128460,0.421110,0.605475,0.762382,0.056137,2.100923,2.187754,2.490083,1.503404,1.190493,1.122696,1.274017,0.964260,1.124325,1.103217,0.863340,0.693827,0.295339,0.472735,0.312599</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>0.8467914883468088</v>
+      </c>
       <c r="K82" t="inlineStr">
         <is>
           <t>82739.414062,82845.328125,82772.171875,82837.679688,82848.117188,82830.281250,82806.570312,82693.445312,82736.140625,82735.539062,82754.906250,82734.226562,82742.070312,82764.078125,82723.062500,82669.687500,82679.632812,82742.734375,82753.203125,82642.859375,82668.640625,82614.406250,82614.773438,82607.718750</t>
@@ -8536,6 +8592,49 @@
       <c r="M82" t="inlineStr">
         <is>
           <t>82557.343750,82487.570312,82436.070312,82410.023438,82379.859375,82342.046875,82286.562500,82285.609375,82236.085938,82165.375000,82081.210938,82118.765625,82086.992188,82104.468750,82116.078125,82053.593750,81991.492188,81889.562500,81921.375000,81901.460938,81897.828125,81770.273438,81783.906250,81767.515625</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-09 05:49:41</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>24</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>82272.226562,82295.773438,82267.257812,82270.359375,82262.984375,82254.390625,82249.484375,82241.437500,82195.453125,82192.085938,82139.562500,82150.929688,82105.835938,82129.609375,82106.195312,82092.906250,82044.031250,82049.125000,82061.132812,82044.671875,82042.828125,82007.460938,81970.906250,81996.171875</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>82258.835938,82342.953125,82243.515625,82266.312500,82290.156250,82254.789062,82290.273438,82205.796875,82200.992188,82216.890625,82165.242188,82155.046875,82238.460938,82187.484375,82167.828125,82124.726562,82087.046875,82193.445312,82148.585938,82076.328125,82099.953125,82009.898438,82019.828125,82019.671875</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>81769.500000,81704.546875,81548.265625,81492.632812,81414.625000,81354.929688,81332.203125,81288.375000,81177.078125,81114.750000,81002.203125,81007.296875,80909.531250,80912.679688,80849.671875,80754.953125,80693.070312,80652.289062,80553.953125,80529.132812,80508.875000,80456.406250,80407.093750,80408.648438</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>81988.468750,81917.648438,81805.078125,81758.351562,81722.703125,81665.125000,81642.062500,81614.000000,81580.757812,81501.156250,81391.734375,81427.031250,81345.921875,81339.828125,81342.046875,81269.398438,81185.265625,81103.539062,81122.781250,81102.898438,81089.531250,80985.390625,80997.742188,81026.742188</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3571,6 +3571,44 @@
       </c>
       <c r="F83" t="n">
         <v>81996.171875</v>
+      </c>
+      <c r="G83" t="n">
+        <v>82662.4296875</v>
+      </c>
+      <c r="H83" t="n">
+        <v>666.2578125</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.8059983417118814</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.5651014708588655</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-10 05:33:03</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>24</v>
+      </c>
+      <c r="F84" t="n">
+        <v>82702.2265625</v>
       </c>
     </row>
   </sheetData>
@@ -3584,7 +3622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8622,6 +8660,24 @@
           <t>82272.226562,82295.773438,82267.257812,82270.359375,82262.984375,82254.390625,82249.484375,82241.437500,82195.453125,82192.085938,82139.562500,82150.929688,82105.835938,82129.609375,82106.195312,82092.906250,82044.031250,82049.125000,82061.132812,82044.671875,82042.828125,82007.460938,81970.906250,81996.171875</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>82512.750000,82591.273438,82626.226562,82580.250000,82487.046875,83175.109375,82954.062500,82553.570312,82962.882812,82807.476562,82679.468750,82643.617188,82369.109375,82251.968750,82431.359375,82465.992188,82561.031250,82544.710938,82489.179688,82620.906250,82551.382812,82519.921875,82614.273438,82662.429688</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>240.523438,295.499999,358.968751,309.890625,224.062500,920.718750,704.578125,312.132812,767.429688,615.390624,539.906250,492.687499,263.273437,122.359375,325.164063,373.085938,517.000000,495.585938,428.046876,576.234375,508.554688,512.460937,643.367188,666.257812</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>0.291499,0.357786,0.434449,0.375260,0.271634,1.106964,0.849359,0.378097,0.925028,0.743158,0.653011,0.596159,0.319626,0.148762,0.394466,0.452412,0.626203,0.600385,0.518913,0.697444,0.616046,0.621015,0.778760,0.805998</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>0.5651014708588655</v>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
           <t>82258.835938,82342.953125,82243.515625,82266.312500,82290.156250,82254.789062,82290.273438,82205.796875,82200.992188,82216.890625,82165.242188,82155.046875,82238.460938,82187.484375,82167.828125,82124.726562,82087.046875,82193.445312,82148.585938,82076.328125,82099.953125,82009.898438,82019.828125,82019.671875</t>
@@ -8635,6 +8691,49 @@
       <c r="M83" t="inlineStr">
         <is>
           <t>81988.468750,81917.648438,81805.078125,81758.351562,81722.703125,81665.125000,81642.062500,81614.000000,81580.757812,81501.156250,81391.734375,81427.031250,81345.921875,81339.828125,81342.046875,81269.398438,81185.265625,81103.539062,81122.781250,81102.898438,81089.531250,80985.390625,80997.742188,81026.742188</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-10 05:33:03</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>24</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>82665.554688,82682.929688,82672.570312,82680.453125,82704.335938,82688.296875,82692.398438,82685.898438,82682.187500,82693.937500,82677.273438,82671.937500,82687.671875,82693.460938,82706.335938,82704.203125,82706.304688,82734.789062,82713.515625,82712.437500,82724.617188,82723.671875,82689.718750,82702.226562</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>82643.468750,82681.554688,82640.484375,82669.476562,82706.265625,82686.867188,82649.375000,82606.453125,82651.351562,82712.906250,82652.054688,82619.890625,82745.796875,82668.421875,82701.593750,82709.242188,82706.476562,82763.335938,82741.312500,82691.335938,82675.101562,82725.015625,82646.468750,82633.625000</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>82270.640625,82245.960938,82141.000000,82110.789062,82057.703125,82006.218750,82004.453125,81946.875000,81875.843750,81822.609375,81768.125000,81717.000000,81660.109375,81663.703125,81621.117188,81535.734375,81515.593750,81499.164062,81349.398438,81310.093750,81283.359375,81267.218750,81215.531250,81191.718750</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>82450.164062,82402.289062,82319.054688,82296.750000,82301.265625,82243.234375,82236.023438,82209.210938,82222.703125,82159.382812,82111.078125,82078.085938,82066.789062,82058.312500,82070.742188,82014.507812,81985.453125,81958.867188,81906.359375,81899.156250,81861.031250,81821.523438,81797.273438,81793.968750</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3609,6 +3609,44 @@
       </c>
       <c r="F84" t="n">
         <v>82702.2265625</v>
+      </c>
+      <c r="G84" t="n">
+        <v>82986.7265625</v>
+      </c>
+      <c r="H84" t="n">
+        <v>284.5</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.3428259093768855</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.2245150230135785</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-11 05:28:15</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>24</v>
+      </c>
+      <c r="F85" t="n">
+        <v>83029.140625</v>
       </c>
     </row>
   </sheetData>
@@ -3622,7 +3660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8721,6 +8759,24 @@
           <t>82665.554688,82682.929688,82672.570312,82680.453125,82704.335938,82688.296875,82692.398438,82685.898438,82682.187500,82693.937500,82677.273438,82671.937500,82687.671875,82693.460938,82706.335938,82704.203125,82706.304688,82734.789062,82713.515625,82712.437500,82724.617188,82723.671875,82689.718750,82702.226562</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>82669.312500,82734.570312,82772.273438,82781.929688,82783.242188,82800.687500,82737.210938,82755.210938,82894.882812,82974.351562,82939.679688,83025.859375,82947.429688,83004.609375,82957.257812,82973.140625,83017.328125,82910.640625,82873.320312,82947.851562,83012.000000,82732.093750,82934.367188,82986.726562</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>3.757812,51.640624,99.703126,101.476562,78.906249,112.390625,44.812499,69.312499,212.695312,280.414062,262.406249,353.921875,259.757812,311.148437,250.921874,268.937500,311.023437,175.851563,159.804688,235.414062,287.382812,8.421875,244.648438,284.500001</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>0.004546,0.062417,0.120455,0.122583,0.095317,0.135736,0.054162,0.083756,0.256584,0.337953,0.316382,0.426279,0.313160,0.374857,0.302471,0.324126,0.374649,0.212098,0.192830,0.283810,0.346194,0.010180,0.294990,0.342826</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>0.2245150230135785</v>
+      </c>
       <c r="K84" t="inlineStr">
         <is>
           <t>82643.468750,82681.554688,82640.484375,82669.476562,82706.265625,82686.867188,82649.375000,82606.453125,82651.351562,82712.906250,82652.054688,82619.890625,82745.796875,82668.421875,82701.593750,82709.242188,82706.476562,82763.335938,82741.312500,82691.335938,82675.101562,82725.015625,82646.468750,82633.625000</t>
@@ -8734,6 +8790,49 @@
       <c r="M84" t="inlineStr">
         <is>
           <t>82450.164062,82402.289062,82319.054688,82296.750000,82301.265625,82243.234375,82236.023438,82209.210938,82222.703125,82159.382812,82111.078125,82078.085938,82066.789062,82058.312500,82070.742188,82014.507812,81985.453125,81958.867188,81906.359375,81899.156250,81861.031250,81821.523438,81797.273438,81793.968750</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-11 05:28:15</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>24</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>82963.609375,82977.765625,82973.835938,82986.929688,82997.968750,82979.476562,82999.914062,82984.960938,82980.742188,82978.117188,82984.054688,82959.281250,82979.679688,82981.015625,82992.750000,82963.656250,83006.226562,83001.929688,83001.265625,82989.648438,82989.773438,83027.906250,83006.125000,83029.140625</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>82946.960938,82932.882812,82972.984375,83017.171875,83035.101562,82970.250000,82980.906250,82934.671875,82961.351562,83002.398438,83006.773438,82967.367188,83004.875000,82948.632812,82986.734375,83007.164062,83032.656250,83033.632812,83041.140625,83019.632812,82989.320312,83073.640625,83001.609375,83000.273438</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>82680.601562,82661.796875,82597.179688,82596.734375,82551.140625,82508.976562,82502.750000,82456.187500,82414.789062,82383.843750,82341.570312,82277.000000,82258.023438,82279.117188,82219.203125,82142.054688,82151.515625,82126.828125,82016.609375,81978.359375,81954.796875,81967.250000,81925.679688,81939.812500</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>82820.312500,82782.062500,82735.843750,82738.500000,82727.859375,82677.507812,82675.468750,82667.226562,82686.765625,82645.765625,82600.070312,82563.617188,82581.820312,82553.632812,82559.421875,82498.750000,82542.335938,82509.695312,82472.789062,82447.312500,82406.507812,82410.648438,82371.375000,82391.984375</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3647,6 +3647,44 @@
       </c>
       <c r="F85" t="n">
         <v>83029.140625</v>
+      </c>
+      <c r="G85" t="n">
+        <v>83804.3203125</v>
+      </c>
+      <c r="H85" t="n">
+        <v>775.1796875</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.9249877388294701</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.5426533385401273</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:39:23</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>24</v>
+      </c>
+      <c r="F86" t="n">
+        <v>83906.0625</v>
       </c>
     </row>
   </sheetData>
@@ -3660,7 +3698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8820,6 +8858,24 @@
           <t>82963.609375,82977.765625,82973.835938,82986.929688,82997.968750,82979.476562,82999.914062,82984.960938,82980.742188,82978.117188,82984.054688,82959.281250,82979.679688,82981.015625,82992.750000,82963.656250,83006.226562,83001.929688,83001.265625,82989.648438,82989.773438,83027.906250,83006.125000,83029.140625</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>83081.968750,82941.070312,82956.570312,82961.117188,82918.031250,83074.468750,83024.281250,82991.750000,83046.820312,83815.710938,83816.367188,83741.523438,83595.187500,83574.953125,83590.132812,83440.562500,83554.132812,83680.593750,83864.273438,83564.968750,83739.687500,83504.710938,84032.812500,83804.320312</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>118.359375,36.695312,17.265626,25.812501,79.937500,94.992188,24.367188,6.789062,66.078124,837.593749,832.312499,782.242188,615.507812,593.937500,597.382812,476.906250,547.906251,678.664062,863.007812,575.320312,749.914062,476.804688,1026.687500,775.179688</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>0.142461,0.044243,0.020813,0.031114,0.096405,0.114346,0.029349,0.008180,0.079567,0.999328,0.993019,0.934115,0.736296,0.710664,0.714657,0.571552,0.655750,0.811017,1.029053,0.688471,0.895530,0.570991,1.221770,0.924988</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>0.5426533385401273</v>
+      </c>
       <c r="K85" t="inlineStr">
         <is>
           <t>82946.960938,82932.882812,82972.984375,83017.171875,83035.101562,82970.250000,82980.906250,82934.671875,82961.351562,83002.398438,83006.773438,82967.367188,83004.875000,82948.632812,82986.734375,83007.164062,83032.656250,83033.632812,83041.140625,83019.632812,82989.320312,83073.640625,83001.609375,83000.273438</t>
@@ -8833,6 +8889,49 @@
       <c r="M85" t="inlineStr">
         <is>
           <t>82820.312500,82782.062500,82735.843750,82738.500000,82727.859375,82677.507812,82675.468750,82667.226562,82686.765625,82645.765625,82600.070312,82563.617188,82581.820312,82553.632812,82559.421875,82498.750000,82542.335938,82509.695312,82472.789062,82447.312500,82406.507812,82410.648438,82371.375000,82391.984375</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:39:23</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>24</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>83736.640625,83739.140625,83762.140625,83769.226562,83802.570312,83797.757812,83831.546875,83800.781250,83802.859375,83816.429688,83849.140625,83825.289062,83856.265625,83839.664062,83857.031250,83845.429688,83897.015625,83897.273438,83893.531250,83896.515625,83875.335938,83886.203125,83895.500000,83906.062500</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>83748.210938,83743.203125,83772.578125,83797.640625,83799.328125,83796.882812,83773.398438,83746.421875,83790.117188,83836.656250,83864.031250,83789.734375,83807.789062,83784.562500,83834.554688,83861.625000,83904.734375,83840.445312,83909.312500,83878.101562,83854.406250,83916.132812,83891.515625,83840.406250</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>83378.585938,83311.507812,83268.929688,83255.718750,83224.265625,83180.343750,83189.031250,83121.367188,83081.453125,83046.046875,83021.781250,82979.328125,82945.906250,82918.742188,82855.773438,82800.703125,82823.906250,82790.015625,82645.773438,82598.226562,82577.671875,82581.398438,82527.281250,82514.265625</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>83556.109375,83486.554688,83445.984375,83452.187500,83434.898438,83405.703125,83416.906250,83378.828125,83381.359375,83354.351562,83335.937500,83319.007812,83326.195312,83291.359375,83281.265625,83242.085938,83291.375000,83244.359375,83194.445312,83177.007812,83121.867188,83100.203125,83075.867188,83090.554688</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3685,6 +3685,44 @@
       </c>
       <c r="F86" t="n">
         <v>83906.0625</v>
+      </c>
+      <c r="G86" t="n">
+        <v>83576.0234375</v>
+      </c>
+      <c r="H86" t="n">
+        <v>330.0390625</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.3948968243826658</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1.265898970513581</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:35:39</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>24</v>
+      </c>
+      <c r="F87" t="n">
+        <v>84004.3046875</v>
       </c>
     </row>
   </sheetData>
@@ -3698,7 +3736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8919,6 +8957,24 @@
           <t>83736.640625,83739.140625,83762.140625,83769.226562,83802.570312,83797.757812,83831.546875,83800.781250,83802.859375,83816.429688,83849.140625,83825.289062,83856.265625,83839.664062,83857.031250,83845.429688,83897.015625,83897.273438,83893.531250,83896.515625,83875.335938,83886.203125,83895.500000,83906.062500</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>84124.992188,83903.687500,83415.007812,83463.343750,83418.718750,83315.773438,82676.906250,82883.203125,82491.460938,82630.210938,82395.578125,82399.000000,82331.710938,82758.078125,82985.476562,82472.617188,82052.421875,81742.500000,81338.523438,82353.500000,82823.671875,83229.757812,83351.476562,83576.023438</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>388.351562,164.546875,347.132812,305.882812,383.851562,481.984374,1154.640625,917.578125,1311.398438,1186.218751,1453.562500,1426.289062,1524.554688,1081.585937,871.554688,1372.812501,1844.593750,2154.773438,2555.007812,1543.015625,1051.664063,656.445312,544.023438,330.039062</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>0.461636,0.196114,0.416152,0.366488,0.460150,0.578503,1.396570,1.107074,1.589738,1.435575,1.764127,1.730954,1.851722,1.306925,1.050250,1.664568,2.248067,2.636050,3.141203,1.873649,1.269763,0.788715,0.652686,0.394897</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>1.265898970513581</v>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
           <t>83748.210938,83743.203125,83772.578125,83797.640625,83799.328125,83796.882812,83773.398438,83746.421875,83790.117188,83836.656250,83864.031250,83789.734375,83807.789062,83784.562500,83834.554688,83861.625000,83904.734375,83840.445312,83909.312500,83878.101562,83854.406250,83916.132812,83891.515625,83840.406250</t>
@@ -8932,6 +8988,49 @@
       <c r="M86" t="inlineStr">
         <is>
           <t>83556.109375,83486.554688,83445.984375,83452.187500,83434.898438,83405.703125,83416.906250,83378.828125,83381.359375,83354.351562,83335.937500,83319.007812,83326.195312,83291.359375,83281.265625,83242.085938,83291.375000,83244.359375,83194.445312,83177.007812,83121.867188,83100.203125,83075.867188,83090.554688</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:35:39</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>24</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>83637.437500,83701.671875,83715.343750,83721.937500,83733.445312,83751.609375,83760.796875,83770.070312,83784.148438,83778.000000,83781.062500,83785.960938,83807.906250,83811.531250,83853.125000,83866.679688,83905.984375,83906.507812,83919.968750,83942.453125,83925.132812,83933.414062,83975.656250,84004.304688</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>83646.015625,83676.148438,83728.640625,83695.656250,83692.382812,83736.617188,83697.500000,83720.554688,83752.148438,83777.882812,83772.015625,83712.593750,83783.820312,83764.156250,83836.070312,83817.281250,83859.515625,83888.750000,83901.601562,83892.242188,83895.609375,83861.437500,83968.078125,84003.851562</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>83139.523438,83092.421875,82986.671875,82948.203125,82877.140625,82832.953125,82803.679688,82718.242188,82705.656250,82629.718750,82578.109375,82515.382812,82508.195312,82424.960938,82430.046875,82381.289062,82377.593750,82361.937500,82254.125000,82257.429688,82264.343750,82238.625000,82261.835938,82247.031250</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>83336.765625,83318.914062,83250.593750,83236.546875,83192.843750,83156.367188,83141.617188,83094.484375,83109.515625,83040.968750,83003.109375,83006.789062,82979.156250,82932.812500,82972.554688,82939.843750,82944.976562,82915.140625,82887.093750,82916.421875,82901.976562,82865.953125,82897.390625,82904.101562</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3723,6 +3723,44 @@
       </c>
       <c r="F87" t="n">
         <v>84004.3046875</v>
+      </c>
+      <c r="G87" t="n">
+        <v>83770.96875</v>
+      </c>
+      <c r="H87" t="n">
+        <v>233.3359375</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.2785403356100021</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.5278484110397763</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-10-14 04:36:17</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>24</v>
+      </c>
+      <c r="F88" t="n">
+        <v>83990.75</v>
       </c>
     </row>
   </sheetData>
@@ -3736,7 +3774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9018,6 +9056,24 @@
           <t>83637.437500,83701.671875,83715.343750,83721.937500,83733.445312,83751.609375,83760.796875,83770.070312,83784.148438,83778.000000,83781.062500,83785.960938,83807.906250,83811.531250,83853.125000,83866.679688,83905.984375,83906.507812,83919.968750,83942.453125,83925.132812,83933.414062,83975.656250,84004.304688</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>83765.718750,83485.617188,83531.437500,83247.101562,83250.078125,83257.289062,83174.367188,83426.617188,83337.531250,83290.000000,83001.039062,83049.250000,83205.437500,83354.187500,83461.968750,83456.843750,83101.992188,83337.562500,83247.539062,83556.390625,83626.703125,83770.968750,83770.968750,83770.968750</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>128.281250,216.054688,183.906250,474.835938,483.367187,494.320312,586.429688,343.453124,446.617188,488.000000,780.023438,736.710938,602.468750,457.343750,391.156250,409.835938,803.992188,568.945312,672.429688,386.062500,298.429687,162.445312,204.687500,233.335938</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>0.153143,0.258793,0.220164,0.570393,0.580621,0.593726,0.705061,0.411683,0.535914,0.585905,0.939776,0.887077,0.724074,0.548675,0.468664,0.491075,0.967476,0.682700,0.807747,0.462038,0.356859,0.193916,0.244342,0.278540</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>0.5278484110397763</v>
+      </c>
       <c r="K87" t="inlineStr">
         <is>
           <t>83646.015625,83676.148438,83728.640625,83695.656250,83692.382812,83736.617188,83697.500000,83720.554688,83752.148438,83777.882812,83772.015625,83712.593750,83783.820312,83764.156250,83836.070312,83817.281250,83859.515625,83888.750000,83901.601562,83892.242188,83895.609375,83861.437500,83968.078125,84003.851562</t>
@@ -9031,6 +9087,49 @@
       <c r="M87" t="inlineStr">
         <is>
           <t>83336.765625,83318.914062,83250.593750,83236.546875,83192.843750,83156.367188,83141.617188,83094.484375,83109.515625,83040.968750,83003.109375,83006.789062,82979.156250,82932.812500,82972.554688,82939.843750,82944.976562,82915.140625,82887.093750,82916.421875,82901.976562,82865.953125,82897.390625,82904.101562</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-10-14 04:36:17</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>24</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>83726.875000,83744.570312,83745.453125,83764.531250,83784.507812,83775.843750,83773.906250,83780.679688,83762.726562,83760.640625,83750.617188,83763.859375,83781.507812,83769.109375,83806.218750,83836.828125,83854.859375,83875.140625,83880.617188,83909.437500,83915.578125,83934.007812,83955.976562,83990.750000</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>83722.281250,83698.648438,83755.445312,83785.945312,83777.000000,83736.546875,83783.500000,83756.257812,83732.562500,83738.515625,83737.460938,83699.359375,83764.945312,83762.875000,83818.625000,83784.921875,83889.976562,83874.695312,83882.375000,83873.109375,83919.250000,83898.343750,83932.335938,83971.367188</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>83334.343750,83295.226562,83219.687500,83229.234375,83190.218750,83143.203125,83117.218750,83070.765625,83005.726562,82953.304688,82893.039062,82869.859375,82831.859375,82799.789062,82807.640625,82793.992188,82782.593750,82799.132812,82693.304688,82702.992188,82713.343750,82688.765625,82664.601562,82665.695312</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>83495.554688,83468.554688,83422.843750,83420.828125,83409.898438,83363.960938,83360.507812,83340.679688,83310.156250,83249.593750,83204.734375,83215.375000,83199.093750,83159.382812,83197.828125,83213.726562,83211.609375,83194.179688,83178.898438,83218.125000,83198.398438,83176.914062,83174.140625,83194.140625</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3761,6 +3761,44 @@
       </c>
       <c r="F88" t="n">
         <v>83990.75</v>
+      </c>
+      <c r="G88" t="n">
+        <v>80932.1328125</v>
+      </c>
+      <c r="H88" t="n">
+        <v>3058.6171875</v>
+      </c>
+      <c r="I88" t="n">
+        <v>3.779237098058529</v>
+      </c>
+      <c r="J88" t="n">
+        <v>2.055245562035418</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-10-15 04:18:51</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>24</v>
+      </c>
+      <c r="F89" t="n">
+        <v>81097.328125</v>
       </c>
     </row>
   </sheetData>
@@ -3774,7 +3812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9117,6 +9155,24 @@
           <t>83726.875000,83744.570312,83745.453125,83764.531250,83784.507812,83775.843750,83773.906250,83780.679688,83762.726562,83760.640625,83750.617188,83763.859375,83781.507812,83769.109375,83806.218750,83836.828125,83854.859375,83875.140625,83880.617188,83909.437500,83915.578125,83934.007812,83955.976562,83990.750000</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>83381.156250,83345.492188,83487.023438,83347.679688,83158.328125,83389.601562,83383.671875,82643.960938,82289.007812,81881.406250,81545.281250,81915.867188,81493.523438,81619.132812,81736.367188,81685.687500,81671.289062,81557.046875,81566.281250,81556.296875,81531.742188,81415.750000,80824.382812,80932.132812</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>345.718750,399.078124,258.429688,416.851562,626.179687,386.242188,390.234375,1136.718751,1473.718749,1879.234375,2205.335938,1847.992188,2287.984374,2149.976562,2069.851562,2151.140625,2183.570312,2318.093750,2314.335938,2353.140625,2383.835938,2518.257812,3131.593749,3058.617188</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>0.414625,0.478824,0.309545,0.500136,0.752997,0.463178,0.467999,1.375441,1.790906,2.295069,2.704431,2.255964,2.807566,2.634158,2.532351,2.633436,2.673608,2.842297,2.837368,2.885296,2.923813,3.093084,3.874566,3.779237</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>2.055245562035418</v>
+      </c>
       <c r="K88" t="inlineStr">
         <is>
           <t>83722.281250,83698.648438,83755.445312,83785.945312,83777.000000,83736.546875,83783.500000,83756.257812,83732.562500,83738.515625,83737.460938,83699.359375,83764.945312,83762.875000,83818.625000,83784.921875,83889.976562,83874.695312,83882.375000,83873.109375,83919.250000,83898.343750,83932.335938,83971.367188</t>
@@ -9130,6 +9186,49 @@
       <c r="M88" t="inlineStr">
         <is>
           <t>83495.554688,83468.554688,83422.843750,83420.828125,83409.898438,83363.960938,83360.507812,83340.679688,83310.156250,83249.593750,83204.734375,83215.375000,83199.093750,83159.382812,83197.828125,83213.726562,83211.609375,83194.179688,83178.898438,83218.125000,83198.398438,83176.914062,83174.140625,83194.140625</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-10-15 04:18:51</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>24</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>80956.421875,80957.921875,80952.343750,80938.812500,80957.476562,80944.320312,80963.695312,80956.320312,80948.296875,80936.820312,80952.343750,80967.921875,80979.781250,81004.937500,81013.984375,81059.718750,81030.125000,81083.562500,81090.812500,81104.132812,81077.734375,81111.343750,81085.796875,81097.328125</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>80965.312500,81031.109375,80922.742188,80971.109375,81002.531250,81051.375000,81053.125000,80920.726562,81036.578125,81050.539062,81013.945312,81025.906250,81103.101562,81082.695312,81165.343750,81108.242188,81167.765625,81249.203125,81236.843750,81258.921875,81205.476562,81117.390625,81193.234375,81266.937500</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>80503.992188,80422.468750,80334.421875,80295.289062,80228.929688,80192.375000,80192.664062,80105.171875,80070.062500,79999.796875,80012.750000,80003.640625,79966.968750,79923.468750,79919.531250,79870.835938,79843.132812,79839.703125,79739.804688,79711.304688,79694.437500,79698.664062,79691.687500,79670.421875</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>80670.500000,80607.281250,80533.710938,80495.359375,80492.117188,80454.984375,80443.328125,80391.109375,80415.414062,80309.812500,80302.820312,80355.960938,80300.773438,80295.960938,80329.859375,80312.078125,80288.531250,80252.343750,80284.500000,80285.218750,80235.343750,80252.937500,80222.156250,80216.484375</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3799,6 +3799,44 @@
       </c>
       <c r="F89" t="n">
         <v>81097.328125</v>
+      </c>
+      <c r="G89" t="n">
+        <v>81954.3671875</v>
+      </c>
+      <c r="H89" t="n">
+        <v>857.0390625</v>
+      </c>
+      <c r="I89" t="n">
+        <v>1.045751546759205</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.9943948736586864</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:14:26</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>24</v>
+      </c>
+      <c r="F90" t="n">
+        <v>81909.96875</v>
       </c>
     </row>
   </sheetData>
@@ -3812,7 +3850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9216,6 +9254,24 @@
           <t>80956.421875,80957.921875,80952.343750,80938.812500,80957.476562,80944.320312,80963.695312,80956.320312,80948.296875,80936.820312,80952.343750,80967.921875,80979.781250,81004.937500,81013.984375,81059.718750,81030.125000,81083.562500,81090.812500,81104.132812,81077.734375,81111.343750,81085.796875,81097.328125</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>80487.476562,80801.468750,81432.031250,81268.351562,81161.257812,80934.640625,80868.398438,80451.968750,80086.281250,81781.281250,82338.953125,82022.539062,82338.937500,82315.156250,82299.250000,82015.617188,82336.109375,82369.968750,82116.203125,82231.468750,81974.820312,81935.773438,82008.156250,81954.367188</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>468.945312,156.453125,479.687500,329.539062,203.781251,9.679687,95.296874,504.351562,862.015625,844.460938,1386.609375,1054.617188,1359.156250,1310.218750,1285.265625,955.898438,1305.984375,1286.406250,1025.390625,1127.335938,897.085938,824.429688,922.359375,857.039062</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>0.582631,0.193627,0.589065,0.405495,0.251082,0.011960,0.117842,0.626898,1.076359,1.032585,1.684026,1.285765,1.650685,1.591710,1.561698,1.165508,1.586162,1.561742,1.248707,1.370930,1.094343,1.006190,1.124717,1.045752</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>0.9943948736586864</v>
+      </c>
       <c r="K89" t="inlineStr">
         <is>
           <t>80965.312500,81031.109375,80922.742188,80971.109375,81002.531250,81051.375000,81053.125000,80920.726562,81036.578125,81050.539062,81013.945312,81025.906250,81103.101562,81082.695312,81165.343750,81108.242188,81167.765625,81249.203125,81236.843750,81258.921875,81205.476562,81117.390625,81193.234375,81266.937500</t>
@@ -9229,6 +9285,49 @@
       <c r="M89" t="inlineStr">
         <is>
           <t>80670.500000,80607.281250,80533.710938,80495.359375,80492.117188,80454.984375,80443.328125,80391.109375,80415.414062,80309.812500,80302.820312,80355.960938,80300.773438,80295.960938,80329.859375,80312.078125,80288.531250,80252.343750,80284.500000,80285.218750,80235.343750,80252.937500,80222.156250,80216.484375</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:14:26</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>24</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>81940.859375,81949.187500,81934.085938,81917.218750,81929.656250,81934.945312,81911.906250,81938.570312,81923.875000,81910.257812,81933.710938,81931.906250,81925.351562,81953.968750,81961.718750,81965.375000,81961.078125,81979.093750,81979.812500,81940.921875,81929.226562,81912.484375,81892.640625,81909.968750</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>81926.000000,81906.656250,81960.359375,81947.312500,81941.601562,81951.171875,81872.609375,81939.304688,81911.335938,81909.460938,81907.687500,81935.078125,81925.953125,81947.617188,82032.210938,81991.015625,81948.804688,81980.265625,81977.328125,81968.406250,81955.867188,81917.820312,81852.921875,81928.789062</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>81497.734375,81395.671875,81270.992188,81194.031250,81159.820312,81122.171875,81030.718750,80993.070312,80924.460938,80829.703125,80854.414062,80820.890625,80774.718750,80755.679688,80745.906250,80688.140625,80644.226562,80634.609375,80512.648438,80455.742188,80439.976562,80392.203125,80373.328125,80327.234375</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>81665.726562,81601.570312,81507.664062,81463.031250,81451.664062,81420.203125,81375.296875,81352.070312,81337.796875,81249.656250,81236.671875,81266.484375,81212.375000,81219.515625,81244.945312,81228.843750,81165.984375,81121.734375,81113.859375,81067.898438,81044.632812,81001.531250,81000.906250,80997.171875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3837,6 +3837,44 @@
       </c>
       <c r="F90" t="n">
         <v>81909.96875</v>
+      </c>
+      <c r="G90" t="n">
+        <v>81411.8671875</v>
+      </c>
+      <c r="H90" t="n">
+        <v>498.1015625</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.6118291837636155</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.4704750211340403</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-10-17 04:04:33</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>24</v>
+      </c>
+      <c r="F91" t="n">
+        <v>81335.515625</v>
       </c>
     </row>
   </sheetData>
@@ -3850,7 +3888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9315,6 +9353,24 @@
           <t>81940.859375,81949.187500,81934.085938,81917.218750,81929.656250,81934.945312,81911.906250,81938.570312,81923.875000,81910.257812,81933.710938,81931.906250,81925.351562,81953.968750,81961.718750,81965.375000,81961.078125,81979.093750,81979.812500,81940.921875,81929.226562,81912.484375,81892.640625,81909.968750</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>82052.156250,82079.843750,82186.203125,82139.320312,81913.539062,82116.703125,82528.976562,81942.773438,81919.351562,81865.117188,81240.078125,81334.000000,81088.703125,81018.742188,81467.500000,81611.343750,81561.289062,81666.640625,81500.039062,81443.093750,81413.523438,81352.031250,81450.742188,81411.867188</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>111.296875,130.656250,252.117187,222.101562,16.117188,181.757813,617.070312,4.203126,4.523438,45.140624,693.632813,597.906250,836.648437,935.226562,494.218750,354.031250,399.789062,312.453125,479.773438,497.828125,515.703124,560.453125,441.898438,498.101562</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>0.135642,0.159182,0.306763,0.270396,0.019676,0.221341,0.747701,0.005129,0.005522,0.055140,0.853806,0.735125,1.031769,1.154334,0.606645,0.433802,0.490170,0.382596,0.588679,0.611259,0.633437,0.688923,0.542535,0.611829</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>0.4704750211340403</v>
+      </c>
       <c r="K90" t="inlineStr">
         <is>
           <t>81926.000000,81906.656250,81960.359375,81947.312500,81941.601562,81951.171875,81872.609375,81939.304688,81911.335938,81909.460938,81907.687500,81935.078125,81925.953125,81947.617188,82032.210938,81991.015625,81948.804688,81980.265625,81977.328125,81968.406250,81955.867188,81917.820312,81852.921875,81928.789062</t>
@@ -9328,6 +9384,49 @@
       <c r="M90" t="inlineStr">
         <is>
           <t>81665.726562,81601.570312,81507.664062,81463.031250,81451.664062,81420.203125,81375.296875,81352.070312,81337.796875,81249.656250,81236.671875,81266.484375,81212.375000,81219.515625,81244.945312,81228.843750,81165.984375,81121.734375,81113.859375,81067.898438,81044.632812,81001.531250,81000.906250,80997.171875</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-10-17 04:04:33</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>24</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>81383.171875,81411.328125,81411.085938,81411.953125,81413.218750,81414.781250,81390.851562,81386.718750,81361.546875,81364.007812,81356.984375,81341.984375,81340.687500,81356.273438,81355.484375,81364.695312,81355.250000,81378.140625,81370.375000,81353.117188,81341.335938,81327.468750,81328.429688,81335.515625</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>81403.078125,81378.453125,81408.093750,81447.007812,81423.750000,81415.960938,81397.304688,81391.078125,81427.203125,81378.320312,81385.406250,81426.507812,81373.343750,81362.390625,81408.062500,81376.953125,81449.859375,81424.921875,81379.328125,81416.273438,81419.242188,81359.671875,81362.664062,81419.250000</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>81043.617188,80988.023438,80916.250000,80869.570312,80814.953125,80777.929688,80688.046875,80628.703125,80593.312500,80532.046875,80514.960938,80463.125000,80421.250000,80416.492188,80366.125000,80324.453125,80281.953125,80270.062500,80159.398438,80138.242188,80079.523438,80004.117188,79990.046875,79971.890625</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>81177.226562,81165.390625,81114.429688,81085.945312,81041.203125,81024.015625,80987.265625,80944.109375,80933.000000,80868.890625,80827.296875,80841.390625,80802.554688,80786.320312,80808.421875,80787.882812,80744.460938,80712.945312,80699.320312,80668.859375,80628.976562,80587.265625,80562.468750,80544.140625</t>
         </is>
       </c>
     </row>
